--- a/Admit_Card_Data_2026.xlsx
+++ b/Admit_Card_Data_2026.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Data" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Admit_Data'!$A$1:$M$270</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Admit_Data'!$A$1:$M$285</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Separate'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Review'!$A$1:$D$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Review'!$A$1:$D$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Centre_Map'!$A$1:$C$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Data'!$A$1:$S$271</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Data'!$A$1:$S$286</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M270"/>
+  <dimension ref="A1:M285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16153,8 +16153,883 @@
         </is>
       </c>
     </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>3843</v>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>41126048</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>Admit_41126048_Duplicate</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>Safwan Zaman Ahnaf</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>Md Shahiduzzaman</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>Delta School and College</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>+8801850401816</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr">
+        <is>
+          <t>Dewanhat</t>
+        </is>
+      </c>
+      <c r="K271" s="2" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L271" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M271" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate of order 3561 (same name &amp; father, different mobile)</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>3844</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>83126042</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Admit_83126042</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Twasin Alam</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Md. Khurshidul Alam</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Chattogram Collegiate School</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>8</v>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>+8801815287418</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>Halishahar</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>3846</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>71126054</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Admit_71126054</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Md.Ridowan Bin Arif</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Md.Ariful Islam</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>মোঃ আরিফুল ইসলাম</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>7</v>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>+8801722966006</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>Dewanhat</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Seven</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>3847</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>51126060</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Admit_51126060</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>AHMAD JAHEE</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>JALAL UDDIN</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>CHATTOGRAM COLLEGIATE SCHOOL</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>5</v>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>+8801626914730</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Dewanhat</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>FIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>3848</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>72226059</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Admit_72226059</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Nusrat Jahan</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Mohammed Jafor Iqbal Talukder</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>CDDL Navy School</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>7</v>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>+8801336826867</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>Patenga</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>3849</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>93126020</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Admit_93126020</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Md.Samiul Islam Alvi</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Md Saiful Islam</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Ispahani Public School And College</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>9</v>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>+8801717944271</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>Agrabad</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>3850</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>61226058</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Admit_61226058</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Tasnia Farin Yusha</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Mohammad Mojibul Hoque</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Dr. Khastagir Govt. Girls High School</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>6</v>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>+8801970433883</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Dewanhat</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>3852</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>62126067</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Admit_62126067</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Prantik Barua Dhrubo</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Dipak Barua</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Green Bell School &amp; College</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>6</v>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>+8801612938480</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Patenga</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Class Six</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>3853</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>71126055</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Admit_71126055</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>MD.Rayhan Alam</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Jahangir Alam</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Chattogram Collegiate School, Chattogram</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>7</v>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>+8801851911435</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Dewanhat</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>3854</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>53226123</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Admit_53226123</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Fahmida khanom alifa</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Ayub khan</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>South kattali pran hori model gov't primary school</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>5</v>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>+8801789865054</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>Halishahar</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>3856</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>73126050</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Admit_73126050</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Mosaidul Hossain Nihad</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Moazzam Hossain Molla</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Halishahar Cantonment Public School and College</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>7</v>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>+8801675271093</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>Halishahar</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Seven</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>3857</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>63226077</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Admit_63226077</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Junaira Farisha Islam</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Me.Manirul Islam</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>HCPSC</t>
+        </is>
+      </c>
+      <c r="H282" t="n">
+        <v>6</v>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>+8801838518567</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>Halishahar</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Six</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>3858</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>43126087</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Admit_43126087</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Zain Riyasat Islam</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Md.Manirul Islam</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>HCPSC</t>
+        </is>
+      </c>
+      <c r="H283" t="n">
+        <v>4</v>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>+8801838518567</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>Halishahar</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Four</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>3860</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>71226068</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Admit_71226068</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Olin Atfa</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>MD. YEASIN ARAFAT</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>GUL-E-ZAR BEGUM CITY CORP MUSLIM GIRLS HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="H284" t="n">
+        <v>7</v>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>+8801866358979</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>Dewanhat</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Seven</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>3861</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>51126061</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Admit_51126061</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>AFSAN NAZRUL AR-RAFI</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>MD. NAZRUL ISLAM</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Ispahani Public School &amp; College</t>
+        </is>
+      </c>
+      <c r="H285" t="n">
+        <v>5</v>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>+8801953031941</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>Dewanhat</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M270"/>
+  <autoFilter ref="A1:M285"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16328,7 +17203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16461,7 +17336,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3750</v>
+        <v>3843</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -16470,18 +17345,18 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MOHAMMED MUHTASIM ISLAM</t>
+          <t>Safwan Zaman Ahnaf</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>same student as order 3506 - kept both, marked in file name</t>
+          <t>likely same student as order 3561 - kept, marked in file name</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3506</v>
+        <v>3750</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -16495,27 +17370,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>same student as order 3750 - kept both, marked in file name</t>
+          <t>same student as order 3506 - kept both, marked in file name</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3446</v>
+        <v>3506</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নুরুল ইসলাম</t>
+          <t>MOHAMMED MUHTASIM ISLAM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>written in Bangla (kept as entered)</t>
+          <t>same student as order 3750 - kept both, marked in file name</t>
         </is>
       </c>
     </row>
@@ -16525,12 +17400,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ডাঃ খাস্তগীর সরকারি বালিকা উচ্চ বিদ্যালয়</t>
+          <t>মোহাম্মদ নুরুল ইসলাম</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -16541,7 +17416,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3509</v>
+        <v>3446</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -16550,7 +17425,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ফুলকি সহজপাঠ বিদ্যালয়</t>
+          <t>ডাঃ খাস্তগীর সরকারি বালিকা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -16561,16 +17436,16 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3604</v>
+        <v>3509</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>মোঃ আনোয়ার হোসেন</t>
+          <t>ফুলকি সহজপাঠ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -16585,12 +17460,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>হালিশহর ক্যান্টনম্যান্ট পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>মোঃ আনোয়ার হোসেন</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -16601,16 +17476,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3639</v>
+        <v>3604</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>মোঃ আবু সায়েম</t>
+          <t>হালিশহর ক্যান্টনম্যান্ট পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -16625,12 +17500,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>মোঃ আবু সায়েম</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -16641,16 +17516,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3642</v>
+        <v>3639</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>মনির হোসেন</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -16665,12 +17540,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>মনির হোসেন</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -16681,16 +17556,16 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>মো: রেজাউল করিম</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -16705,12 +17580,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>মো: রেজাউল করিম</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -16721,16 +17596,16 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3649</v>
+        <v>3643</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>মোঃ নিজাম উদ্দিন</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -16745,12 +17620,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>বাংলাদেশ নৌবাহিনী স্কুল এন্ড কলেজ, চট্টগ্রাম</t>
+          <t>মোঃ নিজাম উদ্দিন</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -16761,16 +17636,16 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3670</v>
+        <v>3649</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>জুলফিকার আলী মিঠু</t>
+          <t>বাংলাদেশ নৌবাহিনী স্কুল এন্ড কলেজ, চট্টগ্রাম</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -16785,12 +17660,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>জুলফিকার আলী মিঠু</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -16801,7 +17676,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3680</v>
+        <v>3670</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -16810,7 +17685,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>বলুয়ারদীঘি সিটি কর্পোরেশন বালিকা উচ্চ বিদ্যালয়</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -16821,16 +17696,16 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3697</v>
+        <v>3680</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>কাকন চক্রবর্তী</t>
+          <t>বলুয়ারদীঘি সিটি কর্পোরেশন বালিকা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -16845,12 +17720,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>মুসলিম এডুকেশন সোসাইটি উচ্চ বিদ্যালয়</t>
+          <t>কাকন চক্রবর্তী</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -16861,16 +17736,16 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3718</v>
+        <v>3697</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>মনির আহমদ</t>
+          <t>মুসলিম এডুকেশন সোসাইটি উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -16885,12 +17760,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>হাটহাজারী আনোয়ারুল উলুম নোমানীয়া ফাজিল মাদ্রাসা</t>
+          <t>মনির আহমদ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -16901,16 +17776,16 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3724</v>
+        <v>3718</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>মনিরুল হক</t>
+          <t>হাটহাজারী আনোয়ারুল উলুম নোমানীয়া ফাজিল মাদ্রাসা</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -16925,12 +17800,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>বাহমনিখীল সরকারি প্রাথমিক বিদ্যালয়</t>
+          <t>মনিরুল হক</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -16941,16 +17816,16 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3748</v>
+        <v>3724</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>আবু বক্কর সিদ্দিক</t>
+          <t>বাহমনিখীল সরকারি প্রাথমিক বিদ্যালয়</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -16965,12 +17840,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>হালিশহর ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>আবু বক্কর সিদ্দিক</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -16981,16 +17856,16 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3770</v>
+        <v>3748</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>মোহাম্মদ রেজাউল করিম</t>
+          <t>হালিশহর ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -17005,12 +17880,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>রেলওয়ে পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>মোহাম্মদ রেজাউল করিম</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -17021,16 +17896,16 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3773</v>
+        <v>3770</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>মোহাম্মদ রেজাউল করিম</t>
+          <t>রেলওয়ে পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -17045,12 +17920,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>সেন্ট্রাল পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>মোহাম্মদ রেজাউল করিম</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -17061,16 +17936,16 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3796</v>
+        <v>3773</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নওশাদ ইকবাল</t>
+          <t>সেন্ট্রাল পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -17085,12 +17960,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
+          <t>মোহাম্মদ নওশাদ ইকবাল</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -17101,16 +17976,16 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নওশাদ ইকবাল</t>
+          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -17125,12 +18000,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
+          <t>মোহাম্মদ নওশাদ ইকবাল</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -17141,16 +18016,16 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3835</v>
+        <v>3797</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>মো ইউসুফ</t>
+          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -17165,12 +18040,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>সি এম পি স্কুল এন্ড কলেজ</t>
+          <t>মো ইউসুফ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -17181,16 +18056,16 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>3840</v>
+        <v>3835</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>শাহা জাহান</t>
+          <t>সি এম পি স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -17205,22 +18080,62 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>Fathers Name</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>শাহা জাহান</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>written in Bangla (kept as entered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>3840</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>Name of School</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>বাকলিয়া আদর্শ বালিকা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>written in Bangla (kept as entered)</t>
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>3846</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Name of School</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>মোঃ আরিফুল ইসলাম</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>written in Bangla (kept as entered)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D44"/>
+  <autoFilter ref="A1:D46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17268,7 +18183,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3">
@@ -17283,7 +18198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4">
@@ -17298,7 +18213,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -17313,7 +18228,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -17328,7 +18243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S271"/>
+  <dimension ref="A1:S286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -39574,8 +40489,1238 @@
         </is>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>3843</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>01720601933</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>DJE2WL950U</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>2026-10-14 07:18:02</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Safwan Zaman Ahnaf</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>সাফওয়ান জামান আহনাফ</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Md Shahiduzzaman</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Tahmina Siddeka</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>Delta School and College</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>Bakolia Access Road, Bakolia, Chattogram</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>01850401816</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>dewanhat</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>3844</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>01815287418</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>DJE90HFF6V</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>2026-10-14 16:12:02</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Twasin Alam</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>ত্বসীন আলম</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Md. Khurshidul Alam</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Mst. Yesmin Akter</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>Chattogram Collegiate School</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>Nayabazar, Halishahar, Chattogram.</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>01815287418</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>halishahar</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>3846</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>01722966006</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>DJF712IC31</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:27:59</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Md.Ridowan Bin Arif</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>মোঃ রিদওয়ান বিন আরিফ</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Md.Ariful Islam</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Rikta Akter</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>মোঃ আরিফুল ইসলাম</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>Seven</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>Sadarghat, Chittagong</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>01722966006</t>
+        </is>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>dewanhat</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>3847</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>01319004461</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>DJF01W6ENE</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:38:55</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>AHMAD JAHEE</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>আহমাদ জাহী</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>JALAL UDDIN</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>SHAMIM AKTER</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>CHATTOGRAM COLLEGIATE SCHOOL</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>FIVE</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>30 NO. M M ALI ROAD, LALKHAN BAZAR, VOTAIYA COLONY, DAMPARA-4000, KHULSHI, CHATTOGRAM</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>01626914730</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>dewanhat</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>3848</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>01723088207</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>7659Q5GH</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:33:41</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Nusrat Jahan</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>নুসরাত জাহান</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Mohammed Jafor Iqbal Talukder</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>Saleha Akter</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>CDDL Navy School</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>Rubi cement colony,(Rab 7 এর পাশে),North Patenga,Chattogram</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>01336826867</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>Patenga</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>3849</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>01723088207</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>DJF424TGIU</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:29:33</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Md.Samiul Islam Alvi</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>মো:সামিউল ইসলাম আলভী</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Md Saiful Islam</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Sarmeen Akter</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>Ispahani Public School And College</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>Shah Garibullah Housing Society,Road no.1/1,House no.01,Khulshi. Chattogram</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>01717944271</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>agrabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>3850</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>01521735429</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>DJG53FJD7N</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:34:58</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Tasnia Farin Yusha</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>তাসনিয়া ফারিন ইউশা</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Mohammad Mojibul Hoque</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Nilufer Yeasmin</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>Dr. Khastagir Govt. Girls High School</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>271, Rosulbag C Block, Bakolia, Chattogram</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>8801970433883</t>
+        </is>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>dewanhat</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>3852</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>01612938480</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>DJG93UQR9T</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>2026-10-16 14:29:51</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Prantik Barua Dhrubo</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>প্রান্তিক বড়ুয়া ধ্রুব</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Dipak Barua</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Priya Barua</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>Green Bell School &amp; College</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>Class Six</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>Dhum para Khatgor Pategha Chattagram</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>01612938480</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>Patenga</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>3853</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>01300480754</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>DJG73Z172T</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:29:58</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>MD.Rayhan Alam</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>মোঃ রায়হান আলম</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Jahangir Alam</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Rehana Akther</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>Chattogram Collegiate School, Chattogram</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>AK house 121, Chandanpura, Chawk bazar, Chattogram</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>01851911435</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>dewanhat</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>3854</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>01873029849</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>DJG541N0CZ</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>2026-10-16 16:04:01</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Fahmida khanom alifa</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>ফাহমিদা খানম আলিফা</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Ayub khan</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Firoja akther</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>South kattali pran hori model gov't primary school</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>Sandwip Bhavon,college road,Halishahor, ctg.</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>01789865054</t>
+        </is>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>halishahar</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>3856</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>01675271093</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>DJG544GCDV</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>2026-10-16 16:59:34</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Mosaidul Hossain Nihad</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>মোসাইদুল হোসেন নিহাদ</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Moazzam Hossain Molla</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Tania Akter</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>Halishahar Cantonment Public School and College</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>Seven</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>Lane-2, I-Block, Halishahar, Chattogram</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>01675271093</t>
+        </is>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>halishahar</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>3857</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>01723088207</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>2026-10-17 15:50:24</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Junaira Farisha Islam</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>জুনাইরা ফারিশা ইসলাম</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Me.Manirul Islam</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Farhana Akter</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>HCPSC</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>Six</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>House #34, Lane#8, Road# 1,Block# A.Halishahar, ctg</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>01838518567</t>
+        </is>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>halishahar</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>3858</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>01723088207</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>2026-10-17 15:59:10</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Zain Riyasat Islam</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>জাইন রিয়াসাত ইসলাম</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Md.Manirul Islam</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Farhana Akter</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>HCPSC</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>Four</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>House #34, Lane#8, Road# 1,Block# A.Halishahar, ctg</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>01838518567</t>
+        </is>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>halishahar</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>3860</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>01836831037</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>DJI469U57W</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:22:09</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Olin Atfa</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>অলিন আতফা</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>MD. YEASIN ARAFAT</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>SABRIN KHANAM</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>GUL-E-ZAR BEGUM CITY CORP MUSLIM GIRLS HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>Seven</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>DC road , chawkbazar, Chittagong</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>01866358979</t>
+        </is>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>dewanhat</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>3861</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>01722212464</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>766HHM4N</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:29:09</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>AFSAN NAZRUL AR-RAFI</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>আফসান নজরুল আর-রাফি</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>MD. NAZRUL ISLAM</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>KANICH FATIMA</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>Ispahani Public School &amp; College</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>Kusumbag R/A, Goribullah shah majar, Khulshi, Chattogram</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>01953031941</t>
+        </is>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>dewanhat</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S271"/>
+  <autoFilter ref="A1:S286"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Admit_Card_Data_2026.xlsx
+++ b/Admit_Card_Data_2026.xlsx
@@ -16159,12 +16159,12 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>41126048</t>
+          <t>41126040</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Admit_41126048_Duplicate</t>
+          <t>Admit_41126040_Duplicate</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>83126042</t>
+          <t>81126057</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Admit_83126042</t>
+          <t>Admit_81126057</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -16280,12 +16280,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>71126054</t>
+          <t>71126059</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Admit_71126054</t>
+          <t>Admit_71126059</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -16338,12 +16338,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>51126060</t>
+          <t>51126067</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Admit_51126060</t>
+          <t>Admit_51126067</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -16396,12 +16396,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>72226059</t>
+          <t>72226069</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Admit_72226059</t>
+          <t>Admit_72226069</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -16454,12 +16454,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>93126020</t>
+          <t>91126020</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Admit_93126020</t>
+          <t>Admit_91126020</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -16497,7 +16497,7 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -16512,12 +16512,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>61226058</t>
+          <t>61226065</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Admit_61226058</t>
+          <t>Admit_61226065</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -16570,12 +16570,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>62126067</t>
+          <t>62126074</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Admit_62126067</t>
+          <t>Admit_62126074</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -16628,12 +16628,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>71126055</t>
+          <t>71126060</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Admit_71126055</t>
+          <t>Admit_71126060</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -16686,12 +16686,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>53226123</t>
+          <t>51226084</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Admit_53226123</t>
+          <t>Admit_51226084</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -16729,7 +16729,7 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -16744,12 +16744,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>73126050</t>
+          <t>71126061</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Admit_73126050</t>
+          <t>Admit_71126061</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -16802,12 +16802,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>63226077</t>
+          <t>61226066</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Admit_63226077</t>
+          <t>Admit_61226066</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -16845,7 +16845,7 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -16860,12 +16860,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>43126087</t>
+          <t>41126054</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Admit_43126087</t>
+          <t>Admit_41126054</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -16903,7 +16903,7 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -16918,12 +16918,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>71226068</t>
+          <t>71226070</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Admit_71226068</t>
+          <t>Admit_71226070</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -16976,12 +16976,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>51126061</t>
+          <t>51126068</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Admit_51126061</t>
+          <t>Admit_51126068</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">

--- a/Admit_Card_Data_2026.xlsx
+++ b/Admit_Card_Data_2026.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Admit_Data'!$A$1:$M$285</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Separate'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Review'!$A$1:$D$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Review'!$A$1:$D$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Centre_Map'!$A$1:$C$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Data'!$A$1:$S$286</definedName>
   </definedNames>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hossain Mohiuddin</t>
+          <t>Sarah Nur Shawli</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -17203,7 +17203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17356,27 +17356,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3750</v>
+        <v>3578</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Name (English)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MOHAMMED MUHTASIM ISLAM</t>
+          <t>Hossain Mohiuddin</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>same student as order 3506 - kept both, marked in file name</t>
+          <t>name corrected to Sarah Nur Shawli (by user)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3506</v>
+        <v>3750</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -17390,27 +17390,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>same student as order 3750 - kept both, marked in file name</t>
+          <t>same student as order 3506 - kept both, marked in file name</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3446</v>
+        <v>3506</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নুরুল ইসলাম</t>
+          <t>MOHAMMED MUHTASIM ISLAM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>written in Bangla (kept as entered)</t>
+          <t>same student as order 3750 - kept both, marked in file name</t>
         </is>
       </c>
     </row>
@@ -17420,12 +17420,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ডাঃ খাস্তগীর সরকারি বালিকা উচ্চ বিদ্যালয়</t>
+          <t>মোহাম্মদ নুরুল ইসলাম</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -17436,7 +17436,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3509</v>
+        <v>3446</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ফুলকি সহজপাঠ বিদ্যালয়</t>
+          <t>ডাঃ খাস্তগীর সরকারি বালিকা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -17456,16 +17456,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3604</v>
+        <v>3509</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>মোঃ আনোয়ার হোসেন</t>
+          <t>ফুলকি সহজপাঠ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -17480,12 +17480,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>হালিশহর ক্যান্টনম্যান্ট পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>মোঃ আনোয়ার হোসেন</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -17496,16 +17496,16 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3639</v>
+        <v>3604</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>মোঃ আবু সায়েম</t>
+          <t>হালিশহর ক্যান্টনম্যান্ট পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -17520,12 +17520,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>মোঃ আবু সায়েম</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -17536,16 +17536,16 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3642</v>
+        <v>3639</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>মনির হোসেন</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -17560,12 +17560,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>মনির হোসেন</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -17576,16 +17576,16 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>মো: রেজাউল করিম</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -17600,12 +17600,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>মো: রেজাউল করিম</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -17616,16 +17616,16 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3649</v>
+        <v>3643</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>মোঃ নিজাম উদ্দিন</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -17640,12 +17640,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>বাংলাদেশ নৌবাহিনী স্কুল এন্ড কলেজ, চট্টগ্রাম</t>
+          <t>মোঃ নিজাম উদ্দিন</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -17656,16 +17656,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3670</v>
+        <v>3649</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>জুলফিকার আলী মিঠু</t>
+          <t>বাংলাদেশ নৌবাহিনী স্কুল এন্ড কলেজ, চট্টগ্রাম</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -17680,12 +17680,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>জুলফিকার আলী মিঠু</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -17696,7 +17696,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3680</v>
+        <v>3670</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>বলুয়ারদীঘি সিটি কর্পোরেশন বালিকা উচ্চ বিদ্যালয়</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -17716,16 +17716,16 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3697</v>
+        <v>3680</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>কাকন চক্রবর্তী</t>
+          <t>বলুয়ারদীঘি সিটি কর্পোরেশন বালিকা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -17740,12 +17740,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>মুসলিম এডুকেশন সোসাইটি উচ্চ বিদ্যালয়</t>
+          <t>কাকন চক্রবর্তী</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -17756,16 +17756,16 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3718</v>
+        <v>3697</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>মনির আহমদ</t>
+          <t>মুসলিম এডুকেশন সোসাইটি উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -17780,12 +17780,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>হাটহাজারী আনোয়ারুল উলুম নোমানীয়া ফাজিল মাদ্রাসা</t>
+          <t>মনির আহমদ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -17796,16 +17796,16 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3724</v>
+        <v>3718</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>মনিরুল হক</t>
+          <t>হাটহাজারী আনোয়ারুল উলুম নোমানীয়া ফাজিল মাদ্রাসা</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -17820,12 +17820,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>বাহমনিখীল সরকারি প্রাথমিক বিদ্যালয়</t>
+          <t>মনিরুল হক</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -17836,16 +17836,16 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3748</v>
+        <v>3724</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>আবু বক্কর সিদ্দিক</t>
+          <t>বাহমনিখীল সরকারি প্রাথমিক বিদ্যালয়</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -17860,12 +17860,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>হালিশহর ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>আবু বক্কর সিদ্দিক</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -17876,16 +17876,16 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3770</v>
+        <v>3748</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>মোহাম্মদ রেজাউল করিম</t>
+          <t>হালিশহর ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -17900,12 +17900,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>রেলওয়ে পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>মোহাম্মদ রেজাউল করিম</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -17916,16 +17916,16 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3773</v>
+        <v>3770</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>মোহাম্মদ রেজাউল করিম</t>
+          <t>রেলওয়ে পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -17940,12 +17940,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>সেন্ট্রাল পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>মোহাম্মদ রেজাউল করিম</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -17956,16 +17956,16 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3796</v>
+        <v>3773</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নওশাদ ইকবাল</t>
+          <t>সেন্ট্রাল পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -17980,12 +17980,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
+          <t>মোহাম্মদ নওশাদ ইকবাল</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -17996,16 +17996,16 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নওশাদ ইকবাল</t>
+          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -18020,12 +18020,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
+          <t>মোহাম্মদ নওশাদ ইকবাল</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -18036,16 +18036,16 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3835</v>
+        <v>3797</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>মো ইউসুফ</t>
+          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -18060,12 +18060,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>সি এম পি স্কুল এন্ড কলেজ</t>
+          <t>মো ইউসুফ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -18076,16 +18076,16 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3840</v>
+        <v>3835</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>শাহা জাহান</t>
+          <t>সি এম পি স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -18100,12 +18100,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>বাকলিয়া আদর্শ বালিকা উচ্চ বিদ্যালয়</t>
+          <t>শাহা জাহান</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -18116,26 +18116,46 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
+        <v>3840</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Name of School</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>বাকলিয়া আদর্শ বালিকা উচ্চ বিদ্যালয়</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>written in Bangla (kept as entered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
         <v>3846</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Name of School</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>মোঃ আরিফুল ইসলাম</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>written in Bangla (kept as entered)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D46"/>
+  <autoFilter ref="A1:D47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Admit_Card_Data_2026.xlsx
+++ b/Admit_Card_Data_2026.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Admit_Data'!$A$1:$M$285</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Separate'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Review'!$A$1:$D$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Review'!$A$1:$D$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Centre_Map'!$A$1:$C$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Data'!$A$1:$S$286</definedName>
   </definedNames>
@@ -968,7 +968,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Mohiuddin Rasel</t>
+          <t>Uttar Kattali Alhaz Mostofa Hakim High School</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -17203,7 +17203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17416,21 +17416,21 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3446</v>
+        <v>3507</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নুরুল ইসলাম</t>
+          <t>Mohiuddin Rasel</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>written in Bangla (kept as entered)</t>
+          <t>school corrected to Uttar Kattali Alhaz Mostofa Hakim High School (by user)</t>
         </is>
       </c>
     </row>
@@ -17440,12 +17440,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ডাঃ খাস্তগীর সরকারি বালিকা উচ্চ বিদ্যালয়</t>
+          <t>মোহাম্মদ নুরুল ইসলাম</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -17456,7 +17456,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3509</v>
+        <v>3446</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ফুলকি সহজপাঠ বিদ্যালয়</t>
+          <t>ডাঃ খাস্তগীর সরকারি বালিকা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -17476,16 +17476,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3604</v>
+        <v>3509</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>মোঃ আনোয়ার হোসেন</t>
+          <t>ফুলকি সহজপাঠ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -17500,12 +17500,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>হালিশহর ক্যান্টনম্যান্ট পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>মোঃ আনোয়ার হোসেন</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -17516,16 +17516,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3639</v>
+        <v>3604</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>মোঃ আবু সায়েম</t>
+          <t>হালিশহর ক্যান্টনম্যান্ট পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -17540,12 +17540,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>মোঃ আবু সায়েম</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -17556,16 +17556,16 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3642</v>
+        <v>3639</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>মনির হোসেন</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -17580,12 +17580,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>মনির হোসেন</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -17596,16 +17596,16 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>মো: রেজাউল করিম</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -17620,12 +17620,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>মো: রেজাউল করিম</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -17636,16 +17636,16 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3649</v>
+        <v>3643</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>মোঃ নিজাম উদ্দিন</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -17660,12 +17660,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>বাংলাদেশ নৌবাহিনী স্কুল এন্ড কলেজ, চট্টগ্রাম</t>
+          <t>মোঃ নিজাম উদ্দিন</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -17676,16 +17676,16 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3670</v>
+        <v>3649</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>জুলফিকার আলী মিঠু</t>
+          <t>বাংলাদেশ নৌবাহিনী স্কুল এন্ড কলেজ, চট্টগ্রাম</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>জুলফিকার আলী মিঠু</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -17716,7 +17716,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3680</v>
+        <v>3670</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>বলুয়ারদীঘি সিটি কর্পোরেশন বালিকা উচ্চ বিদ্যালয়</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -17736,16 +17736,16 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3697</v>
+        <v>3680</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>কাকন চক্রবর্তী</t>
+          <t>বলুয়ারদীঘি সিটি কর্পোরেশন বালিকা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -17760,12 +17760,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>মুসলিম এডুকেশন সোসাইটি উচ্চ বিদ্যালয়</t>
+          <t>কাকন চক্রবর্তী</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -17776,16 +17776,16 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3718</v>
+        <v>3697</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>মনির আহমদ</t>
+          <t>মুসলিম এডুকেশন সোসাইটি উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>হাটহাজারী আনোয়ারুল উলুম নোমানীয়া ফাজিল মাদ্রাসা</t>
+          <t>মনির আহমদ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -17816,16 +17816,16 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3724</v>
+        <v>3718</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>মনিরুল হক</t>
+          <t>হাটহাজারী আনোয়ারুল উলুম নোমানীয়া ফাজিল মাদ্রাসা</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -17840,12 +17840,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>বাহমনিখীল সরকারি প্রাথমিক বিদ্যালয়</t>
+          <t>মনিরুল হক</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -17856,16 +17856,16 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3748</v>
+        <v>3724</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>আবু বক্কর সিদ্দিক</t>
+          <t>বাহমনিখীল সরকারি প্রাথমিক বিদ্যালয়</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -17880,12 +17880,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>হালিশহর ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>আবু বক্কর সিদ্দিক</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -17896,16 +17896,16 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3770</v>
+        <v>3748</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>মোহাম্মদ রেজাউল করিম</t>
+          <t>হালিশহর ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -17920,12 +17920,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>রেলওয়ে পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>মোহাম্মদ রেজাউল করিম</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -17936,16 +17936,16 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3773</v>
+        <v>3770</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>মোহাম্মদ রেজাউল করিম</t>
+          <t>রেলওয়ে পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -17960,12 +17960,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>সেন্ট্রাল পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>মোহাম্মদ রেজাউল করিম</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -17976,16 +17976,16 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3796</v>
+        <v>3773</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নওশাদ ইকবাল</t>
+          <t>সেন্ট্রাল পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -18000,12 +18000,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
+          <t>মোহাম্মদ নওশাদ ইকবাল</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -18016,16 +18016,16 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নওশাদ ইকবাল</t>
+          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -18040,12 +18040,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
+          <t>মোহাম্মদ নওশাদ ইকবাল</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -18056,16 +18056,16 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>3835</v>
+        <v>3797</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>মো ইউসুফ</t>
+          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -18080,12 +18080,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>সি এম পি স্কুল এন্ড কলেজ</t>
+          <t>মো ইউসুফ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -18096,16 +18096,16 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3840</v>
+        <v>3835</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>শাহা জাহান</t>
+          <t>সি এম পি স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -18120,12 +18120,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>বাকলিয়া আদর্শ বালিকা উচ্চ বিদ্যালয়</t>
+          <t>শাহা জাহান</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -18136,26 +18136,46 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
+        <v>3840</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Name of School</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>বাকলিয়া আদর্শ বালিকা উচ্চ বিদ্যালয়</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>written in Bangla (kept as entered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
         <v>3846</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Name of School</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>মোঃ আরিফুল ইসলাম</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>written in Bangla (kept as entered)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D47"/>
+  <autoFilter ref="A1:D48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Admit_Card_Data_2026.xlsx
+++ b/Admit_Card_Data_2026.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Admit_Data'!$A$1:$M$285</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Separate'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Review'!$A$1:$D$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Review'!$A$1:$D$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Centre_Map'!$A$1:$C$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Data'!$A$1:$S$286</definedName>
   </definedNames>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>মোঃ আরিফুল ইসলাম</t>
+          <t>Chattogram Collegiate School</t>
         </is>
       </c>
       <c r="H273" t="n">
@@ -17203,7 +17203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17416,7 +17416,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3507</v>
+        <v>3846</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -17425,32 +17425,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mohiuddin Rasel</t>
+          <t>মোঃ আরিফুল ইসলাম</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>school corrected to Uttar Kattali Alhaz Mostofa Hakim High School (by user)</t>
+          <t>school corrected to Chattogram Collegiate School (by user)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3446</v>
+        <v>3507</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নুরুল ইসলাম</t>
+          <t>Mohiuddin Rasel</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>written in Bangla (kept as entered)</t>
+          <t>school corrected to Uttar Kattali Alhaz Mostofa Hakim High School (by user)</t>
         </is>
       </c>
     </row>
@@ -17460,12 +17460,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ডাঃ খাস্তগীর সরকারি বালিকা উচ্চ বিদ্যালয়</t>
+          <t>মোহাম্মদ নুরুল ইসলাম</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -17476,7 +17476,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3509</v>
+        <v>3446</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ফুলকি সহজপাঠ বিদ্যালয়</t>
+          <t>ডাঃ খাস্তগীর সরকারি বালিকা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -17496,16 +17496,16 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3604</v>
+        <v>3509</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>মোঃ আনোয়ার হোসেন</t>
+          <t>ফুলকি সহজপাঠ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -17520,12 +17520,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>হালিশহর ক্যান্টনম্যান্ট পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>মোঃ আনোয়ার হোসেন</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -17536,16 +17536,16 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3639</v>
+        <v>3604</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>মোঃ আবু সায়েম</t>
+          <t>হালিশহর ক্যান্টনম্যান্ট পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -17560,12 +17560,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>মোঃ আবু সায়েম</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -17576,16 +17576,16 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3642</v>
+        <v>3639</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>মনির হোসেন</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -17600,12 +17600,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>মনির হোসেন</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -17616,16 +17616,16 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>মো: রেজাউল করিম</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -17640,12 +17640,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>মো: রেজাউল করিম</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -17656,16 +17656,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3649</v>
+        <v>3643</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>মোঃ নিজাম উদ্দিন</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -17680,12 +17680,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>বাংলাদেশ নৌবাহিনী স্কুল এন্ড কলেজ, চট্টগ্রাম</t>
+          <t>মোঃ নিজাম উদ্দিন</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -17696,16 +17696,16 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3670</v>
+        <v>3649</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>জুলফিকার আলী মিঠু</t>
+          <t>বাংলাদেশ নৌবাহিনী স্কুল এন্ড কলেজ, চট্টগ্রাম</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>জুলফিকার আলী মিঠু</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -17736,7 +17736,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3680</v>
+        <v>3670</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>বলুয়ারদীঘি সিটি কর্পোরেশন বালিকা উচ্চ বিদ্যালয়</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -17756,16 +17756,16 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3697</v>
+        <v>3680</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>কাকন চক্রবর্তী</t>
+          <t>বলুয়ারদীঘি সিটি কর্পোরেশন বালিকা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -17780,12 +17780,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>মুসলিম এডুকেশন সোসাইটি উচ্চ বিদ্যালয়</t>
+          <t>কাকন চক্রবর্তী</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -17796,16 +17796,16 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3718</v>
+        <v>3697</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>মনির আহমদ</t>
+          <t>মুসলিম এডুকেশন সোসাইটি উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -17820,12 +17820,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>হাটহাজারী আনোয়ারুল উলুম নোমানীয়া ফাজিল মাদ্রাসা</t>
+          <t>মনির আহমদ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -17836,16 +17836,16 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3724</v>
+        <v>3718</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>মনিরুল হক</t>
+          <t>হাটহাজারী আনোয়ারুল উলুম নোমানীয়া ফাজিল মাদ্রাসা</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -17860,12 +17860,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>বাহমনিখীল সরকারি প্রাথমিক বিদ্যালয়</t>
+          <t>মনিরুল হক</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -17876,16 +17876,16 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3748</v>
+        <v>3724</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>আবু বক্কর সিদ্দিক</t>
+          <t>বাহমনিখীল সরকারি প্রাথমিক বিদ্যালয়</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -17900,12 +17900,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>হালিশহর ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>আবু বক্কর সিদ্দিক</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -17916,16 +17916,16 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3770</v>
+        <v>3748</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>মোহাম্মদ রেজাউল করিম</t>
+          <t>হালিশহর ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -17940,12 +17940,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>রেলওয়ে পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>মোহাম্মদ রেজাউল করিম</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -17956,16 +17956,16 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3773</v>
+        <v>3770</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>মোহাম্মদ রেজাউল করিম</t>
+          <t>রেলওয়ে পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -17980,12 +17980,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>সেন্ট্রাল পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>মোহাম্মদ রেজাউল করিম</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -17996,16 +17996,16 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3796</v>
+        <v>3773</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নওশাদ ইকবাল</t>
+          <t>সেন্ট্রাল পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -18020,12 +18020,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
+          <t>মোহাম্মদ নওশাদ ইকবাল</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -18036,16 +18036,16 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নওশাদ ইকবাল</t>
+          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -18060,12 +18060,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
+          <t>মোহাম্মদ নওশাদ ইকবাল</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -18076,16 +18076,16 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3835</v>
+        <v>3797</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>মো ইউসুফ</t>
+          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -18100,12 +18100,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>সি এম পি স্কুল এন্ড কলেজ</t>
+          <t>মো ইউসুফ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -18116,16 +18116,16 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3840</v>
+        <v>3835</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>শাহা জাহান</t>
+          <t>সি এম পি স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -18140,12 +18140,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>বাকলিয়া আদর্শ বালিকা উচ্চ বিদ্যালয়</t>
+          <t>শাহা জাহান</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -18156,26 +18156,46 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
+        <v>3840</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Name of School</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>বাকলিয়া আদর্শ বালিকা উচ্চ বিদ্যালয়</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>written in Bangla (kept as entered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
         <v>3846</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Name of School</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>মোঃ আরিফুল ইসলাম</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>written in Bangla (kept as entered)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D48"/>
+  <autoFilter ref="A1:D49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Admit_Card_Data_2026.xlsx
+++ b/Admit_Card_Data_2026.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Admit_Data'!$A$1:$M$285</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Separate'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Review'!$A$1:$D$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Review'!$A$1:$D$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Centre_Map'!$A$1:$C$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Data'!$A$1:$S$286</definedName>
   </definedNames>
@@ -14898,7 +14898,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>M. Jahirul Islam</t>
+          <t>Miskatul Jannat Labiba</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -16063,7 +16063,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Md Absul mannan vhyain</t>
+          <t>Md Abdul mannan vhyain</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -17203,7 +17203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17276,27 +17276,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3600</v>
+        <v>3841</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mobile (Online)</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0183519086</t>
+          <t>Md Absul mannan vhyain</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>invalid mobile (10 digits); replaced with Bkash number +8801835190860</t>
+          <t>father's name corrected to Md Abdul mannan vhyain (by user)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3534</v>
+        <v>3600</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -17305,18 +17305,18 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>101812378354</t>
+          <t>0183519086</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>invalid mobile (12 digits); replaced with Bkash number +8801812378354</t>
+          <t>invalid mobile (10 digits); replaced with Bkash number +8801835190860</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3648</v>
+        <v>3534</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -17325,158 +17325,158 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>017418691933</t>
+          <t>101812378354</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>invalid mobile (12 digits); replaced with Nagad Number +8801819315767 - different number, please confirm</t>
+          <t>invalid mobile (12 digits); replaced with Bkash number +8801812378354</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3843</v>
+        <v>3648</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Mobile (Online)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Safwan Zaman Ahnaf</t>
+          <t>017418691933</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>likely same student as order 3561 - kept, marked in file name</t>
+          <t>invalid mobile (12 digits); replaced with Nagad Number +8801819315767 - different number, please confirm</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3578</v>
+        <v>3843</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Name (English)</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hossain Mohiuddin</t>
+          <t>Safwan Zaman Ahnaf</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>name corrected to Sarah Nur Shawli (by user)</t>
+          <t>likely same student as order 3561 - kept, marked in file name</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3750</v>
+        <v>3795</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Name (English)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MOHAMMED MUHTASIM ISLAM</t>
+          <t>M. Jahirul Islam</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>same student as order 3506 - kept both, marked in file name</t>
+          <t>name corrected to Miskatul Jannat Labiba (by user)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3506</v>
+        <v>3578</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Name (English)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MOHAMMED MUHTASIM ISLAM</t>
+          <t>Hossain Mohiuddin</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>same student as order 3750 - kept both, marked in file name</t>
+          <t>name corrected to Sarah Nur Shawli (by user)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3846</v>
+        <v>3750</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>মোঃ আরিফুল ইসলাম</t>
+          <t>MOHAMMED MUHTASIM ISLAM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>school corrected to Chattogram Collegiate School (by user)</t>
+          <t>same student as order 3506 - kept both, marked in file name</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mohiuddin Rasel</t>
+          <t>MOHAMMED MUHTASIM ISLAM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>school corrected to Uttar Kattali Alhaz Mostofa Hakim High School (by user)</t>
+          <t>same student as order 3750 - kept both, marked in file name</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3446</v>
+        <v>3846</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নুরুল ইসলাম</t>
+          <t>মোঃ আরিফুল ইসলাম</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>written in Bangla (kept as entered)</t>
+          <t>school corrected to Chattogram Collegiate School (by user)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3446</v>
+        <v>3507</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -17485,27 +17485,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ডাঃ খাস্তগীর সরকারি বালিকা উচ্চ বিদ্যালয়</t>
+          <t>Mohiuddin Rasel</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>written in Bangla (kept as entered)</t>
+          <t>school corrected to Uttar Kattali Alhaz Mostofa Hakim High School (by user)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3509</v>
+        <v>3446</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ফুলকি সহজপাঠ বিদ্যালয়</t>
+          <t>মোহাম্মদ নুরুল ইসলাম</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -17516,16 +17516,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3604</v>
+        <v>3446</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>মোঃ আনোয়ার হোসেন</t>
+          <t>ডাঃ খাস্তগীর সরকারি বালিকা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -17536,7 +17536,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3604</v>
+        <v>3509</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>হালিশহর ক্যান্টনম্যান্ট পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>ফুলকি সহজপাঠ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -17556,7 +17556,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3639</v>
+        <v>3604</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>মোঃ আবু সায়েম</t>
+          <t>মোঃ আনোয়ার হোসেন</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -17576,7 +17576,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3639</v>
+        <v>3604</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>হালিশহর ক্যান্টনম্যান্ট পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -17596,7 +17596,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3642</v>
+        <v>3639</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>মনির হোসেন</t>
+          <t>মোঃ আবু সায়েম</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -17616,7 +17616,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3642</v>
+        <v>3639</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>মো: রেজাউল করিম</t>
+          <t>মনির হোসেন</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -17656,7 +17656,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -17676,7 +17676,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3649</v>
+        <v>3643</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>মোঃ নিজাম উদ্দিন</t>
+          <t>মো: রেজাউল করিম</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -17696,7 +17696,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3649</v>
+        <v>3643</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>বাংলাদেশ নৌবাহিনী স্কুল এন্ড কলেজ, চট্টগ্রাম</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -17716,7 +17716,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3670</v>
+        <v>3649</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>জুলফিকার আলী মিঠু</t>
+          <t>মোঃ নিজাম উদ্দিন</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -17736,7 +17736,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3670</v>
+        <v>3649</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>বাংলাদেশ নৌবাহিনী স্কুল এন্ড কলেজ, চট্টগ্রাম</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -17756,16 +17756,16 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3680</v>
+        <v>3670</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>বলুয়ারদীঘি সিটি কর্পোরেশন বালিকা উচ্চ বিদ্যালয়</t>
+          <t>জুলফিকার আলী মিঠু</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -17776,16 +17776,16 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3697</v>
+        <v>3670</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>কাকন চক্রবর্তী</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -17796,7 +17796,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3697</v>
+        <v>3680</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>মুসলিম এডুকেশন সোসাইটি উচ্চ বিদ্যালয়</t>
+          <t>বলুয়ারদীঘি সিটি কর্পোরেশন বালিকা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -17816,7 +17816,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3718</v>
+        <v>3697</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>মনির আহমদ</t>
+          <t>কাকন চক্রবর্তী</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -17836,7 +17836,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3718</v>
+        <v>3697</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>হাটহাজারী আনোয়ারুল উলুম নোমানীয়া ফাজিল মাদ্রাসা</t>
+          <t>মুসলিম এডুকেশন সোসাইটি উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -17856,7 +17856,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3724</v>
+        <v>3718</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>মনিরুল হক</t>
+          <t>মনির আহমদ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -17876,7 +17876,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3724</v>
+        <v>3718</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>বাহমনিখীল সরকারি প্রাথমিক বিদ্যালয়</t>
+          <t>হাটহাজারী আনোয়ারুল উলুম নোমানীয়া ফাজিল মাদ্রাসা</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -17896,7 +17896,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3748</v>
+        <v>3724</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>আবু বক্কর সিদ্দিক</t>
+          <t>মনিরুল হক</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -17916,7 +17916,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3748</v>
+        <v>3724</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>হালিশহর ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>বাহমনিখীল সরকারি প্রাথমিক বিদ্যালয়</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -17936,7 +17936,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3770</v>
+        <v>3748</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>মোহাম্মদ রেজাউল করিম</t>
+          <t>আবু বক্কর সিদ্দিক</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -17956,7 +17956,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3770</v>
+        <v>3748</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>রেলওয়ে পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>হালিশহর ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -17976,7 +17976,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3773</v>
+        <v>3770</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3773</v>
+        <v>3770</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>সেন্ট্রাল পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>রেলওয়ে পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -18016,7 +18016,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3796</v>
+        <v>3773</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নওশাদ ইকবাল</t>
+          <t>মোহাম্মদ রেজাউল করিম</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -18036,7 +18036,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3796</v>
+        <v>3773</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
+          <t>সেন্ট্রাল পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -18056,7 +18056,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3835</v>
+        <v>3797</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>মো ইউসুফ</t>
+          <t>মোহাম্মদ নওশাদ ইকবাল</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -18116,7 +18116,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3835</v>
+        <v>3797</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>সি এম পি স্কুল এন্ড কলেজ</t>
+          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -18136,7 +18136,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3840</v>
+        <v>3835</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>শাহা জাহান</t>
+          <t>মো ইউসুফ</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -18156,7 +18156,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3840</v>
+        <v>3835</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>বাকলিয়া আদর্শ বালিকা উচ্চ বিদ্যালয়</t>
+          <t>সি এম পি স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -18176,26 +18176,66 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
+        <v>3840</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Fathers Name</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>শাহা জাহান</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>written in Bangla (kept as entered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>3840</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Name of School</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>বাকলিয়া আদর্শ বালিকা উচ্চ বিদ্যালয়</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>written in Bangla (kept as entered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
         <v>3846</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Name of School</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>মোঃ আরিফুল ইসলাম</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>written in Bangla (kept as entered)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D49"/>
+  <autoFilter ref="A1:D51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Admit_Card_Data_2026.xlsx
+++ b/Admit_Card_Data_2026.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Admit_Data'!$A$1:$M$285</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Separate'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Review'!$A$1:$D$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Review'!$A$1:$D$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Centre_Map'!$A$1:$C$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Data'!$A$1:$S$286</definedName>
   </definedNames>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Nazmin Akter</t>
+          <t>Railway public High School</t>
         </is>
       </c>
       <c r="H147" t="n">
@@ -17203,7 +17203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17476,7 +17476,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3507</v>
+        <v>3667</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -17485,32 +17485,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mohiuddin Rasel</t>
+          <t>Nazmin Akter</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>school corrected to Uttar Kattali Alhaz Mostofa Hakim High School (by user)</t>
+          <t>school corrected to Railway public High School (by user)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3446</v>
+        <v>3507</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নুরুল ইসলাম</t>
+          <t>Mohiuddin Rasel</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>written in Bangla (kept as entered)</t>
+          <t>school corrected to Uttar Kattali Alhaz Mostofa Hakim High School (by user)</t>
         </is>
       </c>
     </row>
@@ -17520,12 +17520,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ডাঃ খাস্তগীর সরকারি বালিকা উচ্চ বিদ্যালয়</t>
+          <t>মোহাম্মদ নুরুল ইসলাম</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -17536,7 +17536,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3509</v>
+        <v>3446</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ফুলকি সহজপাঠ বিদ্যালয়</t>
+          <t>ডাঃ খাস্তগীর সরকারি বালিকা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -17556,16 +17556,16 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3604</v>
+        <v>3509</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>মোঃ আনোয়ার হোসেন</t>
+          <t>ফুলকি সহজপাঠ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -17580,12 +17580,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>হালিশহর ক্যান্টনম্যান্ট পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>মোঃ আনোয়ার হোসেন</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -17596,16 +17596,16 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3639</v>
+        <v>3604</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>মোঃ আবু সায়েম</t>
+          <t>হালিশহর ক্যান্টনম্যান্ট পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -17620,12 +17620,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>মোঃ আবু সায়েম</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -17636,16 +17636,16 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3642</v>
+        <v>3639</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>মনির হোসেন</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -17660,12 +17660,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>মনির হোসেন</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -17676,16 +17676,16 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>মো: রেজাউল করিম</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>মো: রেজাউল করিম</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -17716,16 +17716,16 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3649</v>
+        <v>3643</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>মোঃ নিজাম উদ্দিন</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -17740,12 +17740,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>বাংলাদেশ নৌবাহিনী স্কুল এন্ড কলেজ, চট্টগ্রাম</t>
+          <t>মোঃ নিজাম উদ্দিন</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -17756,16 +17756,16 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3670</v>
+        <v>3649</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>জুলফিকার আলী মিঠু</t>
+          <t>বাংলাদেশ নৌবাহিনী স্কুল এন্ড কলেজ, চট্টগ্রাম</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -17780,12 +17780,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>জুলফিকার আলী মিঠু</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -17796,7 +17796,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3680</v>
+        <v>3670</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>বলুয়ারদীঘি সিটি কর্পোরেশন বালিকা উচ্চ বিদ্যালয়</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -17816,16 +17816,16 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3697</v>
+        <v>3680</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>কাকন চক্রবর্তী</t>
+          <t>বলুয়ারদীঘি সিটি কর্পোরেশন বালিকা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -17840,12 +17840,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>মুসলিম এডুকেশন সোসাইটি উচ্চ বিদ্যালয়</t>
+          <t>কাকন চক্রবর্তী</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -17856,16 +17856,16 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3718</v>
+        <v>3697</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>মনির আহমদ</t>
+          <t>মুসলিম এডুকেশন সোসাইটি উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -17880,12 +17880,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>হাটহাজারী আনোয়ারুল উলুম নোমানীয়া ফাজিল মাদ্রাসা</t>
+          <t>মনির আহমদ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -17896,16 +17896,16 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3724</v>
+        <v>3718</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>মনিরুল হক</t>
+          <t>হাটহাজারী আনোয়ারুল উলুম নোমানীয়া ফাজিল মাদ্রাসা</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -17920,12 +17920,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>বাহমনিখীল সরকারি প্রাথমিক বিদ্যালয়</t>
+          <t>মনিরুল হক</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -17936,16 +17936,16 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3748</v>
+        <v>3724</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>আবু বক্কর সিদ্দিক</t>
+          <t>বাহমনিখীল সরকারি প্রাথমিক বিদ্যালয়</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -17960,12 +17960,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>হালিশহর ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>আবু বক্কর সিদ্দিক</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -17976,16 +17976,16 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3770</v>
+        <v>3748</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>মোহাম্মদ রেজাউল করিম</t>
+          <t>হালিশহর ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -18000,12 +18000,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>রেলওয়ে পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>মোহাম্মদ রেজাউল করিম</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -18016,16 +18016,16 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3773</v>
+        <v>3770</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>মোহাম্মদ রেজাউল করিম</t>
+          <t>রেলওয়ে পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -18040,12 +18040,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>সেন্ট্রাল পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>মোহাম্মদ রেজাউল করিম</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -18056,16 +18056,16 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>3796</v>
+        <v>3773</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নওশাদ ইকবাল</t>
+          <t>সেন্ট্রাল পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -18080,12 +18080,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
+          <t>মোহাম্মদ নওশাদ ইকবাল</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -18096,16 +18096,16 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নওশাদ ইকবাল</t>
+          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -18120,12 +18120,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
+          <t>মোহাম্মদ নওশাদ ইকবাল</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -18136,16 +18136,16 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3835</v>
+        <v>3797</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>মো ইউসুফ</t>
+          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -18160,12 +18160,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>সি এম পি স্কুল এন্ড কলেজ</t>
+          <t>মো ইউসুফ</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -18176,16 +18176,16 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3840</v>
+        <v>3835</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>শাহা জাহান</t>
+          <t>সি এম পি স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -18200,12 +18200,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>বাকলিয়া আদর্শ বালিকা উচ্চ বিদ্যালয়</t>
+          <t>শাহা জাহান</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -18216,26 +18216,46 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
+        <v>3840</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Name of School</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>বাকলিয়া আদর্শ বালিকা উচ্চ বিদ্যালয়</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>written in Bangla (kept as entered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
         <v>3846</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Name of School</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>মোঃ আরিফুল ইসলাম</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>written in Bangla (kept as entered)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D51"/>
+  <autoFilter ref="A1:D52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Admit_Card_Data_2026.xlsx
+++ b/Admit_Card_Data_2026.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Admit_Data'!$A$1:$M$285</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Separate'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Review'!$A$1:$D$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Review'!$A$1:$D$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Centre_Map'!$A$1:$C$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Data'!$A$1:$S$286</definedName>
   </definedNames>
@@ -8977,17 +8977,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Nazmin Akter</t>
+          <t>Md.Naquibuddin</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Nazmin Akter</t>
+          <t>Md.Jashim Uddin</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Railway public High School</t>
+          <t>Railway Public High School</t>
         </is>
       </c>
       <c r="H147" t="n">
@@ -17203,7 +17203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17296,27 +17296,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3600</v>
+        <v>3667</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mobile (Online)</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0183519086</t>
+          <t>Nazmin Akter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>invalid mobile (10 digits); replaced with Bkash number +8801835190860</t>
+          <t>father's name corrected to Md.Jashim Uddin (by user)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3534</v>
+        <v>3600</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -17325,18 +17325,18 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>101812378354</t>
+          <t>0183519086</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>invalid mobile (12 digits); replaced with Bkash number +8801812378354</t>
+          <t>invalid mobile (10 digits); replaced with Bkash number +8801835190860</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3648</v>
+        <v>3534</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -17345,58 +17345,58 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>017418691933</t>
+          <t>101812378354</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>invalid mobile (12 digits); replaced with Nagad Number +8801819315767 - different number, please confirm</t>
+          <t>invalid mobile (12 digits); replaced with Bkash number +8801812378354</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3843</v>
+        <v>3648</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Mobile (Online)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Safwan Zaman Ahnaf</t>
+          <t>017418691933</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>likely same student as order 3561 - kept, marked in file name</t>
+          <t>invalid mobile (12 digits); replaced with Nagad Number +8801819315767 - different number, please confirm</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3795</v>
+        <v>3843</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Name (English)</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>M. Jahirul Islam</t>
+          <t>Safwan Zaman Ahnaf</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>name corrected to Miskatul Jannat Labiba (by user)</t>
+          <t>likely same student as order 3561 - kept, marked in file name</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3578</v>
+        <v>3667</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -17405,98 +17405,98 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hossain Mohiuddin</t>
+          <t>Nazmin Akter</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>name corrected to Sarah Nur Shawli (by user)</t>
+          <t>name corrected to Md.Naquibuddin (by user)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3750</v>
+        <v>3795</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Name (English)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MOHAMMED MUHTASIM ISLAM</t>
+          <t>M. Jahirul Islam</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>same student as order 3506 - kept both, marked in file name</t>
+          <t>name corrected to Miskatul Jannat Labiba (by user)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3506</v>
+        <v>3578</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Name (English)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MOHAMMED MUHTASIM ISLAM</t>
+          <t>Hossain Mohiuddin</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>same student as order 3750 - kept both, marked in file name</t>
+          <t>name corrected to Sarah Nur Shawli (by user)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3846</v>
+        <v>3750</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>মোঃ আরিফুল ইসলাম</t>
+          <t>MOHAMMED MUHTASIM ISLAM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>school corrected to Chattogram Collegiate School (by user)</t>
+          <t>same student as order 3506 - kept both, marked in file name</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3667</v>
+        <v>3506</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nazmin Akter</t>
+          <t>MOHAMMED MUHTASIM ISLAM</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>school corrected to Railway public High School (by user)</t>
+          <t>same student as order 3750 - kept both, marked in file name</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3507</v>
+        <v>3846</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -17505,38 +17505,38 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mohiuddin Rasel</t>
+          <t>মোঃ আরিফুল ইসলাম</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>school corrected to Uttar Kattali Alhaz Mostofa Hakim High School (by user)</t>
+          <t>school corrected to Chattogram Collegiate School (by user)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3446</v>
+        <v>3667</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নুরুল ইসলাম</t>
+          <t>Nazmin Akter</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>written in Bangla (kept as entered)</t>
+          <t>school corrected to Railway Public High School (by user)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3446</v>
+        <v>3507</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -17545,27 +17545,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ডাঃ খাস্তগীর সরকারি বালিকা উচ্চ বিদ্যালয়</t>
+          <t>Mohiuddin Rasel</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>written in Bangla (kept as entered)</t>
+          <t>school corrected to Uttar Kattali Alhaz Mostofa Hakim High School (by user)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3509</v>
+        <v>3446</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ফুলকি সহজপাঠ বিদ্যালয়</t>
+          <t>মোহাম্মদ নুরুল ইসলাম</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -17576,16 +17576,16 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3604</v>
+        <v>3446</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>মোঃ আনোয়ার হোসেন</t>
+          <t>ডাঃ খাস্তগীর সরকারি বালিকা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -17596,7 +17596,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3604</v>
+        <v>3509</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>হালিশহর ক্যান্টনম্যান্ট পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>ফুলকি সহজপাঠ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -17616,7 +17616,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3639</v>
+        <v>3604</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -17625,7 +17625,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>মোঃ আবু সায়েম</t>
+          <t>মোঃ আনোয়ার হোসেন</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -17636,7 +17636,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3639</v>
+        <v>3604</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>হালিশহর ক্যান্টনম্যান্ট পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -17656,7 +17656,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3642</v>
+        <v>3639</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>মনির হোসেন</t>
+          <t>মোঃ আবু সায়েম</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -17676,7 +17676,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3642</v>
+        <v>3639</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>মো: রেজাউল করিম</t>
+          <t>মনির হোসেন</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -17716,7 +17716,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3649</v>
+        <v>3643</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>মোঃ নিজাম উদ্দিন</t>
+          <t>মো: রেজাউল করিম</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -17756,7 +17756,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3649</v>
+        <v>3643</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>বাংলাদেশ নৌবাহিনী স্কুল এন্ড কলেজ, চট্টগ্রাম</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -17776,7 +17776,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3670</v>
+        <v>3649</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>জুলফিকার আলী মিঠু</t>
+          <t>মোঃ নিজাম উদ্দিন</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -17796,7 +17796,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3670</v>
+        <v>3649</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>বিএএফ শাহীন কলেজ</t>
+          <t>বাংলাদেশ নৌবাহিনী স্কুল এন্ড কলেজ, চট্টগ্রাম</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -17816,16 +17816,16 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3680</v>
+        <v>3670</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Name of School</t>
+          <t>Fathers Name</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>বলুয়ারদীঘি সিটি কর্পোরেশন বালিকা উচ্চ বিদ্যালয়</t>
+          <t>জুলফিকার আলী মিঠু</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -17836,16 +17836,16 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3697</v>
+        <v>3670</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fathers Name</t>
+          <t>Name of School</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>কাকন চক্রবর্তী</t>
+          <t>বিএএফ শাহীন কলেজ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -17856,7 +17856,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3697</v>
+        <v>3680</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>মুসলিম এডুকেশন সোসাইটি উচ্চ বিদ্যালয়</t>
+          <t>বলুয়ারদীঘি সিটি কর্পোরেশন বালিকা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -17876,7 +17876,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3718</v>
+        <v>3697</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>মনির আহমদ</t>
+          <t>কাকন চক্রবর্তী</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -17896,7 +17896,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3718</v>
+        <v>3697</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>হাটহাজারী আনোয়ারুল উলুম নোমানীয়া ফাজিল মাদ্রাসা</t>
+          <t>মুসলিম এডুকেশন সোসাইটি উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -17916,7 +17916,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3724</v>
+        <v>3718</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>মনিরুল হক</t>
+          <t>মনির আহমদ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -17936,7 +17936,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3724</v>
+        <v>3718</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>বাহমনিখীল সরকারি প্রাথমিক বিদ্যালয়</t>
+          <t>হাটহাজারী আনোয়ারুল উলুম নোমানীয়া ফাজিল মাদ্রাসা</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -17956,7 +17956,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3748</v>
+        <v>3724</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>আবু বক্কর সিদ্দিক</t>
+          <t>মনিরুল হক</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -17976,7 +17976,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3748</v>
+        <v>3724</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>হালিশহর ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>বাহমনিখীল সরকারি প্রাথমিক বিদ্যালয়</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -17996,7 +17996,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3770</v>
+        <v>3748</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>মোহাম্মদ রেজাউল করিম</t>
+          <t>আবু বক্কর সিদ্দিক</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -18016,7 +18016,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3770</v>
+        <v>3748</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>রেলওয়ে পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>হালিশহর ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -18036,7 +18036,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3773</v>
+        <v>3770</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>3773</v>
+        <v>3770</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>সেন্ট্রাল পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>রেলওয়ে পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -18076,7 +18076,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3796</v>
+        <v>3773</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নওশাদ ইকবাল</t>
+          <t>মোহাম্মদ রেজাউল করিম</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -18096,7 +18096,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3796</v>
+        <v>3773</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
+          <t>সেন্ট্রাল পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -18116,7 +18116,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3835</v>
+        <v>3797</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>মো ইউসুফ</t>
+          <t>মোহাম্মদ নওশাদ ইকবাল</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -18176,7 +18176,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3835</v>
+        <v>3797</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>সি এম পি স্কুল এন্ড কলেজ</t>
+          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -18196,7 +18196,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3840</v>
+        <v>3835</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>শাহা জাহান</t>
+          <t>মো ইউসুফ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -18216,7 +18216,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3840</v>
+        <v>3835</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>বাকলিয়া আদর্শ বালিকা উচ্চ বিদ্যালয়</t>
+          <t>সি এম পি স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -18236,26 +18236,66 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
+        <v>3840</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Fathers Name</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>শাহা জাহান</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>written in Bangla (kept as entered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>3840</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Name of School</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>বাকলিয়া আদর্শ বালিকা উচ্চ বিদ্যালয়</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>written in Bangla (kept as entered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
         <v>3846</v>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Name of School</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>মোঃ আরিফুল ইসলাম</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>written in Bangla (kept as entered)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D52"/>
+  <autoFilter ref="A1:D54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Admit_Card_Data_2026.xlsx
+++ b/Admit_Card_Data_2026.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Data" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Admit_Data'!$A$1:$M$285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Admit_Data'!$A$1:$M$299</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Separate'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Review'!$A$1:$D$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Review'!$A$1:$D$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Centre_Map'!$A$1:$C$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Data'!$A$1:$S$286</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Raw_Data'!$A$1:$S$300</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M285"/>
+  <dimension ref="A1:M299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10466,44 +10466,39 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>3696</v>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>13126010</t>
-        </is>
+        <v>3695</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Admit_13126010</t>
+          <t>Admit_3695</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Md Amin Uz Zaman</t>
+          <t>ZAFIRA AHMED</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Md Jashim Uddin</t>
+          <t>ZABED AHMED</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Halishahar Cantonmen Public School and College</t>
+          <t>Silver Bells Kindergarten &amp; Girls' High School</t>
         </is>
       </c>
       <c r="H173" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>+8801627800560</t>
+          <t>+8801911246556</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10513,27 +10508,27 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>Ten</t>
+          <t>SIX</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>3697</v>
+        <v>3696</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>61126051</t>
+          <t>13126010</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Admit_61126051</t>
+          <t>Admit_13126010</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10543,55 +10538,55 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>ANIRUDDHA CHAKRABORTY</t>
+          <t>Md Amin Uz Zaman</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>কাকন চক্রবর্তী</t>
+          <t>Md Jashim Uddin</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>মুসলিম এডুকেশন সোসাইটি উচ্চ বিদ্যালয়</t>
+          <t>Halishahar Cantonmen Public School and College</t>
         </is>
       </c>
       <c r="H174" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>+8801839244671</t>
+          <t>+8801627800560</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Halishahar</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>৬ষ্ঠ</t>
+          <t>Ten</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>3698</v>
+        <v>3697</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>92126033</t>
+          <t>61126051</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Admit_92126033</t>
+          <t>Admit_61126051</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -10601,141 +10596,141 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Mashrur Rahman</t>
+          <t>ANIRUDDHA CHAKRABORTY</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mashiur Rahman</t>
+          <t>কাকন চক্রবর্তী</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Bangladesh Air Force Shaheen College Chattogram</t>
+          <t>মুসলিম এডুকেশন সোসাইটি উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="H175" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>+8801912879833</t>
+          <t>+8801839244671</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Patenga</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>IX</t>
+          <t>৬ষ্ঠ</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>3700</v>
+        <v>3698</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>63226073</t>
+          <t>92126033</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Admit_63226073</t>
+          <t>Admit_92126033</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>MST Afiya Jaman Shifa</t>
+          <t>Mashrur Rahman</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Md Jashim Uddin</t>
+          <t>Mashiur Rahman</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Halishahar Cantonmen Public School and College</t>
+          <t>Bangladesh Air Force Shaheen College Chattogram</t>
         </is>
       </c>
       <c r="H176" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>+8801627800560</t>
+          <t>+8801912879833</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Halishahar</t>
+          <t>Patenga</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Six</t>
+          <t>IX</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>3701</v>
+        <v>3700</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>73126046</t>
+          <t>63226073</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Admit_73126046</t>
+          <t>Admit_63226073</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Fahid Hasan Chowdhury</t>
+          <t>MST Afiya Jaman Shifa</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Forman Ullah Chowdhury</t>
+          <t>Md Jashim Uddin</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Halishahar Cantonment Public School and College</t>
+          <t>Halishahar Cantonmen Public School and College</t>
         </is>
       </c>
       <c r="H177" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>+8801718779294</t>
+          <t>+8801627800560</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10750,22 +10745,22 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>Six</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>3702</v>
+        <v>3701</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>11126022</t>
+          <t>73126046</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Admit_11126022</t>
+          <t>Admit_73126046</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -10775,55 +10770,55 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>MD. Ejaj</t>
+          <t>Fahid Hasan Chowdhury</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>MD. Azizul Hoque</t>
+          <t>Forman Ullah Chowdhury</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Railway Public High School</t>
+          <t>Halishahar Cantonment Public School and College</t>
         </is>
       </c>
       <c r="H178" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>+8801742690738</t>
+          <t>+8801718779294</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Halishahar</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>3703</v>
+        <v>3702</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>43126081</t>
+          <t>11126022</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Admit_43126081</t>
+          <t>Admit_11126022</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -10833,55 +10828,55 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Md.Saad Bin Yusuf</t>
+          <t>MD. Ejaj</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Md.Yusuf Nove</t>
+          <t>MD. Azizul Hoque</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Bhatiary cantonment public school and college</t>
+          <t>Railway Public High School</t>
         </is>
       </c>
       <c r="H179" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>+8801846018495</t>
+          <t>+8801742690738</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Agrabad</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>3704</v>
+        <v>3703</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>61126052</t>
+          <t>43126081</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Admit_61126052</t>
+          <t>Admit_43126081</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -10891,55 +10886,55 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Mohammad Sohail Saad</t>
+          <t>Md.Saad Bin Yusuf</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mohammad Salim</t>
+          <t>Md.Yusuf Nove</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Central Public School &amp; College</t>
+          <t>Bhatiary cantonment public school and college</t>
         </is>
       </c>
       <c r="H180" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>+8801843365631</t>
+          <t>+8801846018495</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Agrabad</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>Six</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>3705</v>
+        <v>3704</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>73126047</t>
+          <t>61126052</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Admit_73126047</t>
+          <t>Admit_61126052</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -10949,55 +10944,55 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>MD SABIT MAHMUD CHOWDHURY</t>
+          <t>Mohammad Sohail Saad</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>MD KAMRUZZAMAN CHOWDHURY</t>
+          <t>Mohammad Salim</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>GARIB E NEWAZ HIGH SCHOOL</t>
+          <t>Central Public School &amp; College</t>
         </is>
       </c>
       <c r="H181" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>+8801763831359</t>
+          <t>+8801843365631</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Halishahar</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>SEVEN</t>
+          <t>Six</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>3707</v>
+        <v>3705</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>71126048</t>
+          <t>73126047</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Admit_71126048</t>
+          <t>Admit_73126047</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11007,17 +11002,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Mohammed Ibtisham Safwan</t>
+          <t>MD SABIT MAHMUD CHOWDHURY</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Muhammed Iqbal Hossain</t>
+          <t>MD KAMRUZZAMAN CHOWDHURY</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Cumilla cadet college</t>
+          <t>GARIB E NEWAZ HIGH SCHOOL</t>
         </is>
       </c>
       <c r="H182" t="n">
@@ -11025,37 +11020,37 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>+8801716640721</t>
+          <t>+8801763831359</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Halishahar</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>Seven</t>
+          <t>SEVEN</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>3708</v>
+        <v>3707</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>63126052</t>
+          <t>71126048</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Admit_63126052</t>
+          <t>Admit_71126048</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11065,88 +11060,88 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Syed Al Wasi</t>
+          <t>Mohammed Ibtisham Safwan</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>S. M. Akhtarul Islam</t>
+          <t>Muhammed Iqbal Hossain</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Kalokakoli High School</t>
+          <t>Cumilla cadet college</t>
         </is>
       </c>
       <c r="H183" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>+8801730597304</t>
+          <t>+8801716640721</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Agrabad</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>Six</t>
+          <t>Seven</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>3709</v>
+        <v>3708</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>73226061</t>
+          <t>63126052</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Admit_73226061</t>
+          <t>Admit_63126052</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Sabiha Binte Azad</t>
+          <t>Syed Al Wasi</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Mohammad Azad Hossain</t>
+          <t>S. M. Akhtarul Islam</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Silver Bells Kindergarten &amp; Girls' High School</t>
+          <t>Kalokakoli High School</t>
         </is>
       </c>
       <c r="H184" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>+8801716800118</t>
+          <t>+8801730597304</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Halishahar</t>
+          <t>Agrabad</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -11156,50 +11151,50 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>Seven</t>
+          <t>Six</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>3710</v>
+        <v>3709</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>43126082</t>
+          <t>73226061</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Admit_43126082</t>
+          <t>Admit_73226061</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Md. Adian Rahman</t>
+          <t>Sabiha Binte Azad</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Md. Motiur Rahman</t>
+          <t>Mohammad Azad Hossain</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Duha International School</t>
+          <t>Silver Bells Kindergarten &amp; Girls' High School</t>
         </is>
       </c>
       <c r="H185" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>+8801795517841</t>
+          <t>+8801716800118</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -11214,22 +11209,22 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>Four</t>
+          <t>Seven</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>3711</v>
+        <v>3710</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>43126083</t>
+          <t>43126082</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Admit_43126083</t>
+          <t>Admit_43126082</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11239,17 +11234,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>MD TAHMID HASAN</t>
+          <t>Md. Adian Rahman</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>MD KAMRUL HASAN</t>
+          <t>Md. Motiur Rahman</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>GOLDEN BELLS PUBLIC SCHOOL</t>
+          <t>Duha International School</t>
         </is>
       </c>
       <c r="H186" t="n">
@@ -11257,12 +11252,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>+8801922529503</t>
+          <t>+8801795517841</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Agrabad</t>
+          <t>Halishahar</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -11272,42 +11267,42 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Four</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>3712</v>
+        <v>3711</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>42226060</t>
+          <t>43126083</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Admit_42226060</t>
+          <t>Admit_43126083</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Afifa Abiat Shamma</t>
+          <t>MD TAHMID HASAN</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>MD. Abu Bakar Siddique</t>
+          <t>MD KAMRUL HASAN</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>BN school and college, Chattogram.</t>
+          <t>GOLDEN BELLS PUBLIC SCHOOL</t>
         </is>
       </c>
       <c r="H187" t="n">
@@ -11315,17 +11310,17 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>+8801301034969</t>
+          <t>+8801922529503</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Patenga</t>
+          <t>Agrabad</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -11336,16 +11331,16 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>3713</v>
+        <v>3712</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>62226064</t>
+          <t>42226060</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Admit_62226064</t>
+          <t>Admit_42226060</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11355,25 +11350,25 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>TASHRIFA FARIHAT RAHEEKA</t>
+          <t>Afifa Abiat Shamma</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>S.M.Manik Hasan</t>
+          <t>MD. Abu Bakar Siddique</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Bangladesh Noubahini School and College, Chattogram</t>
+          <t>BN school and college, Chattogram.</t>
         </is>
       </c>
       <c r="H188" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>+8801731852344</t>
+          <t>+8801301034969</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11388,22 +11383,22 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>3714</v>
+        <v>3713</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>43226082</t>
+          <t>62226064</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Admit_43226082</t>
+          <t>Admit_62226064</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11413,55 +11408,55 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Sawdah Shamim</t>
+          <t>TASHRIFA FARIHAT RAHEEKA</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Md Abdur Rahim</t>
+          <t>S.M.Manik Hasan</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Silver Bells Kindergarten &amp;Girls High School</t>
+          <t>Bangladesh Noubahini School and College, Chattogram</t>
         </is>
       </c>
       <c r="H189" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>+8801742074910</t>
+          <t>+8801731852344</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Halishahar</t>
+          <t>Patenga</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>3715</v>
+        <v>3714</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>41226059</t>
+          <t>43226082</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Admit_41226059</t>
+          <t>Admit_43226082</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -11471,17 +11466,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Syeda Alvina Anhar</t>
+          <t>Sawdah Shamim</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>S.M Shohrab Uddin</t>
+          <t>Md Abdur Rahim</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Aunkur Society Girls' High School</t>
+          <t>Silver Bells Kindergarten &amp;Girls High School</t>
         </is>
       </c>
       <c r="H190" t="n">
@@ -11489,181 +11484,181 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>+8801731229355</t>
+          <t>+8801742074910</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Halishahar</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>Four</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>3717</v>
+        <v>3715</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>53126065</t>
+          <t>41226059</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Admit_53126065</t>
+          <t>Admit_41226059</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Tashfiq Fawaj Uddin</t>
+          <t>Syeda Alvina Anhar</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Md Tareq Muslhe Uddin</t>
+          <t>S.M Shohrab Uddin</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Chattogram Collegiate School</t>
+          <t>Aunkur Society Girls' High School</t>
         </is>
       </c>
       <c r="H191" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>+8801719214978</t>
+          <t>+8801731229355</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Halishahar</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Five</t>
+          <t>Four</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>3718</v>
+        <v>3717</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>41226060</t>
+          <t>53126065</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Admit_41226060</t>
+          <t>Admit_53126065</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>TASFIA AHMED RAISA</t>
+          <t>Tashfiq Fawaj Uddin</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>মনির আহমদ</t>
+          <t>Md Tareq Muslhe Uddin</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>হাটহাজারী আনোয়ারুল উলুম নোমানীয়া ফাজিল মাদ্রাসা</t>
+          <t>Chattogram Collegiate School</t>
         </is>
       </c>
       <c r="H192" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>+8801717032356</t>
+          <t>+8801719214978</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Halishahar</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>৪র্থ শ্রেণি</t>
+          <t>Five</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>3719</v>
+        <v>3718</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>81126046</t>
+          <t>41226060</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Admit_81126046</t>
+          <t>Admit_41226060</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Md. Naban Nawaz</t>
+          <t>TASFIA AHMED RAISA</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Md. Kazi Morsed Nawaz</t>
+          <t>মনির আহমদ</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Chattogram Collegiate School</t>
+          <t>হাটহাজারী আনোয়ারুল উলুম নোমানীয়া ফাজিল মাদ্রাসা</t>
         </is>
       </c>
       <c r="H193" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>+8801818671665</t>
+          <t>+8801717032356</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11678,46 +11673,46 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>Eight</t>
+          <t>৪র্থ শ্রেণি</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>3720</v>
+        <v>3719</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>51226068</t>
+          <t>81126046</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Admit_51226068</t>
+          <t>Admit_81126046</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Nobaira Masiat</t>
+          <t>Md. Naban Nawaz</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Kazi Md Morsed Nawaz</t>
+          <t>Md. Kazi Morsed Nawaz</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Aunkur society girls high school</t>
+          <t>Chattogram Collegiate School</t>
         </is>
       </c>
       <c r="H194" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -11736,22 +11731,22 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>Five</t>
+          <t>Eight</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>3721</v>
+        <v>3720</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>43226083</t>
+          <t>51226068</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Admit_43226083</t>
+          <t>Admit_51226068</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -11761,55 +11756,55 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Tahani Ahmed</t>
+          <t>Nobaira Masiat</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Md Bashir Ahmed</t>
+          <t>Kazi Md Morsed Nawaz</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Khawja Ajmeri Kindergarten and High School</t>
+          <t>Aunkur society girls high school</t>
         </is>
       </c>
       <c r="H195" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>+8801814431675</t>
+          <t>+8801818671665</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Agrabad</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>Five</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>3722</v>
+        <v>3721</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>52226072</t>
+          <t>43226083</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Admit_52226072</t>
+          <t>Admit_43226083</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -11819,55 +11814,55 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Naureen Afsin</t>
+          <t>Tahani Ahmed</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Sazzat Ahmed</t>
+          <t>Md Bashir Ahmed</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Halishahar Begumjan Govt.Primary School</t>
+          <t>Khawja Ajmeri Kindergarten and High School</t>
         </is>
       </c>
       <c r="H196" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>+8801816575436</t>
+          <t>+8801814431675</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Patenga</t>
+          <t>Agrabad</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>Five</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>3724</v>
+        <v>3722</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>51226069</t>
+          <t>52226072</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Admit_51226069</t>
+          <t>Admit_52226072</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -11877,17 +11872,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Ayenan Tajrian</t>
+          <t>Naureen Afsin</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>মনিরুল হক</t>
+          <t>Sazzat Ahmed</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>বাহমনিখীল সরকারি প্রাথমিক বিদ্যালয়</t>
+          <t>Halishahar Begumjan Govt.Primary School</t>
         </is>
       </c>
       <c r="H197" t="n">
@@ -11895,37 +11890,37 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>+8801824875684</t>
+          <t>+8801816575436</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Patenga</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>৫ম</t>
+          <t>Five</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>3725</v>
+        <v>3724</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>61226056</t>
+          <t>51226069</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Admit_61226056</t>
+          <t>Admit_51226069</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -11935,25 +11930,25 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>HUMAIRA BINTE TOFAYEL</t>
+          <t>Ayenan Tajrian</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>TOFAYEL AHAMED BHUIYA</t>
+          <t>মনিরুল হক</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>ISPAHANI PUBLIC SCHOOL AND COLLAGE</t>
+          <t>বাহমনিখীল সরকারি প্রাথমিক বিদ্যালয়</t>
         </is>
       </c>
       <c r="H198" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>+8801826104689</t>
+          <t>+8801824875684</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -11968,80 +11963,80 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>SIX</t>
+          <t>৫ম</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>3727</v>
+        <v>3725</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>83126040</t>
+          <t>61226056</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Admit_83126040</t>
+          <t>Admit_61226056</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Ariz Alam</t>
+          <t>HUMAIRA BINTE TOFAYEL</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Johirul Alam</t>
+          <t>TOFAYEL AHAMED BHUIYA</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Chittagong Collegiate School</t>
+          <t>ISPAHANI PUBLIC SCHOOL AND COLLAGE</t>
         </is>
       </c>
       <c r="H199" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>+8801670654650</t>
+          <t>+8801826104689</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Agrabad</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>SIX</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>3728</v>
+        <v>3727</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>63126053</t>
+          <t>83126040</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Admit_63126053</t>
+          <t>Admit_83126040</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -12051,30 +12046,30 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Pritam Sarker</t>
+          <t>Ariz Alam</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Suman Kumer Sarker</t>
+          <t>Johirul Alam</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Mirza Ahmed Ispahani High School</t>
+          <t>Chittagong Collegiate School</t>
         </is>
       </c>
       <c r="H200" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>+8801313783170</t>
+          <t>+8801670654650</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Halishahar</t>
+          <t>Agrabad</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -12084,22 +12079,22 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>Six</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>3730</v>
+        <v>3728</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>53126066</t>
+          <t>63126053</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Admit_53126066</t>
+          <t>Admit_63126053</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -12109,25 +12104,25 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Nahiyan Bin Habib</t>
+          <t>Pritam Sarker</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Ahsan Habib</t>
+          <t>Suman Kumer Sarker</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Halishahar Cantonment Public School and College</t>
+          <t>Mirza Ahmed Ispahani High School</t>
         </is>
       </c>
       <c r="H201" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>+8801815507501</t>
+          <t>+8801313783170</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -12142,22 +12137,22 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>Five</t>
+          <t>Six</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>3731</v>
+        <v>3730</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>63126054</t>
+          <t>53126066</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Admit_63126054</t>
+          <t>Admit_53126066</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -12167,7 +12162,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Ahiyan Bin Habib</t>
+          <t>Nahiyan Bin Habib</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -12181,7 +12176,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -12200,22 +12195,22 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>Six</t>
+          <t>Five</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>3732</v>
+        <v>3731</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>53126067</t>
+          <t>63126054</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Admit_53126067</t>
+          <t>Admit_63126054</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -12225,30 +12220,30 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>ARIJEET DAS ARPIT</t>
+          <t>Ahiyan Bin Habib</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>RUPAK DAS</t>
+          <t>Ahsan Habib</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>BANGLADESH BANK COLONY HIGH SCHOOL, CHATTOGRAM</t>
+          <t>Halishahar Cantonment Public School and College</t>
         </is>
       </c>
       <c r="H203" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>+8801872612184</t>
+          <t>+8801815507501</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Agrabad</t>
+          <t>Halishahar</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -12258,22 +12253,22 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Six</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>3733</v>
+        <v>3732</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>83126041</t>
+          <t>53126067</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Admit_83126041</t>
+          <t>Admit_53126067</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -12283,7 +12278,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>ABHIJEET DAS AVI</t>
+          <t>ARIJEET DAS ARPIT</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -12297,7 +12292,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -12316,22 +12311,22 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>3734</v>
+        <v>3733</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>63126055</t>
+          <t>83126041</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Admit_63126055</t>
+          <t>Admit_83126041</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -12341,30 +12336,30 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Meraj Islam Shafi</t>
+          <t>ABHIJEET DAS AVI</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Md Shafiqul Islam</t>
+          <t>RUPAK DAS</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Mirza Ahmed Ispahani High School</t>
+          <t>BANGLADESH BANK COLONY HIGH SCHOOL, CHATTOGRAM</t>
         </is>
       </c>
       <c r="H205" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>+8801686489196</t>
+          <t>+8801872612184</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>Halishahar</t>
+          <t>Agrabad</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -12374,108 +12369,108 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>3735</v>
+        <v>3734</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>11226012</t>
+          <t>63126055</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Admit_11226012</t>
+          <t>Admit_63126055</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Nishat Tasnim</t>
+          <t>Meraj Islam Shafi</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Md.Kamal Uddin</t>
+          <t>Md Shafiqul Islam</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Ispahani Public School and College</t>
+          <t>Mirza Ahmed Ispahani High School</t>
         </is>
       </c>
       <c r="H206" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>+8801772512820</t>
+          <t>+8801686489196</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Halishahar</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>Ten</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>3737</v>
+        <v>3735</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>91126011</t>
+          <t>11226012</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Admit_91126011</t>
+          <t>Admit_11226012</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Jahan sani</t>
+          <t>Nishat Tasnim</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Md.Ayub</t>
+          <t>Md.Kamal Uddin</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Orbit Presidential school and College</t>
+          <t>Ispahani Public School and College</t>
         </is>
       </c>
       <c r="H207" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>+8801843191962</t>
+          <t>+8801772512820</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -12490,22 +12485,22 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>Nine</t>
+          <t>Ten</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>3739</v>
+        <v>3737</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>41126045</t>
+          <t>91126011</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Admit_41126045</t>
+          <t>Admit_91126011</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -12515,7 +12510,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>MD.Farhan Mohib Rony</t>
+          <t>Jahan sani</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -12525,11 +12520,11 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Nasirabad Colony Government Primary school</t>
+          <t>Orbit Presidential school and College</t>
         </is>
       </c>
       <c r="H208" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -12548,50 +12543,50 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>Four</t>
+          <t>Nine</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>3742</v>
+        <v>3739</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>11226013</t>
+          <t>41126045</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Admit_11226013</t>
+          <t>Admit_41126045</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Tahira Tabassum Rasin</t>
+          <t>MD.Farhan Mohib Rony</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Md. Shahab Uddin</t>
+          <t>Md.Ayub</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Shah Walimullah Institute, Chottogram</t>
+          <t>Nasirabad Colony Government Primary school</t>
         </is>
       </c>
       <c r="H209" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>+8801609667604</t>
+          <t>+8801843191962</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -12606,22 +12601,22 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Four</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>3748</v>
+        <v>3742</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>63226074</t>
+          <t>11226013</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Admit_63226074</t>
+          <t>Admit_11226013</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -12631,312 +12626,312 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Tamiha Sarkar</t>
+          <t>Tahira Tabassum Rasin</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>আবু বক্কর সিদ্দিক</t>
+          <t>Md. Shahab Uddin</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>হালিশহর ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>Shah Walimullah Institute, Chottogram</t>
         </is>
       </c>
       <c r="H210" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>+8801950603376</t>
+          <t>+8801609667604</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Halishahar</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
+        <v>3748</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>63226074</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Admit_63226074</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Tamiha Sarkar</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>আবু বক্কর সিদ্দিক</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>হালিশহর ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ</t>
+        </is>
+      </c>
+      <c r="H211" t="n">
+        <v>6</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>+8801950603376</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Halishahar</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
         <v>3749</v>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B212" t="inlineStr">
         <is>
           <t>51126054</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
+      <c r="C212" t="inlineStr">
         <is>
           <t>Admit_51126054</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="D212" t="inlineStr">
         <is>
           <t>Boy</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
+      <c r="E212" t="inlineStr">
         <is>
           <t>Hossain Al Jawad</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
+      <c r="F212" t="inlineStr">
         <is>
           <t>Mohammad Deloar Hossan</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="G212" t="inlineStr">
         <is>
           <t>Collegiate school, Chattogram.</t>
         </is>
       </c>
-      <c r="H211" t="n">
+      <c r="H212" t="n">
         <v>5</v>
       </c>
-      <c r="I211" t="inlineStr">
+      <c r="I212" t="inlineStr">
         <is>
           <t>+8801842741420</t>
         </is>
       </c>
-      <c r="J211" t="inlineStr">
+      <c r="J212" t="inlineStr">
         <is>
           <t>Dewanhat</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
+      <c r="K212" t="inlineStr">
         <is>
           <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
+      <c r="L212" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="n">
+    <row r="213">
+      <c r="A213" s="2" t="n">
         <v>3750</v>
       </c>
-      <c r="B212" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
         <is>
           <t>63126056</t>
         </is>
       </c>
-      <c r="C212" s="2" t="inlineStr">
+      <c r="C213" s="2" t="inlineStr">
         <is>
           <t>Admit_63126056_Duplicate</t>
         </is>
       </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>Boy</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>MOHAMMED MUHTASIM ISLAM</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>MOHAMMED NURUL ISLAM MUNNA</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr">
         <is>
           <t>CHATTOGRAM COLLEGIATE SCHOOL</t>
         </is>
       </c>
-      <c r="H212" s="2" t="n">
+      <c r="H213" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="I212" s="2" t="inlineStr">
+      <c r="I213" s="2" t="inlineStr">
         <is>
           <t>+8801921636910</t>
         </is>
       </c>
-      <c r="J212" s="2" t="inlineStr">
+      <c r="J213" s="2" t="inlineStr">
         <is>
           <t>Agrabad</t>
         </is>
       </c>
-      <c r="K212" s="2" t="inlineStr">
+      <c r="K213" s="2" t="inlineStr">
         <is>
           <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
-      <c r="L212" s="2" t="inlineStr">
+      <c r="L213" s="2" t="inlineStr">
         <is>
           <t>SIX</t>
         </is>
       </c>
-      <c r="M212" s="2" t="inlineStr">
+      <c r="M213" s="2" t="inlineStr">
         <is>
           <t>Duplicate of order 3506</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
-        <v>3752</v>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>81126047</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Admit_81126047</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>Boy</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>Al Jawadur Rahman Sowad</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>Mohammed Abul Hossen</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>Central Public School and College</t>
-        </is>
-      </c>
-      <c r="H213" t="n">
-        <v>8</v>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>+8801625444963</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>Dewanhat</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
-        </is>
-      </c>
-      <c r="L213" t="inlineStr">
-        <is>
-          <t>Eight</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>3753</v>
+        <v>3752</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>63226075</t>
+          <t>81126047</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Admit_63226075</t>
+          <t>Admit_81126047</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Fatema Akter Samiya</t>
+          <t>Al Jawadur Rahman Sowad</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Mosaruf hossain</t>
+          <t>Mohammed Abul Hossen</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Silver Bells Kindergarten &amp; Girls' High School</t>
+          <t>Central Public School and College</t>
         </is>
       </c>
       <c r="H214" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>+8801869336887</t>
+          <t>+8801625444963</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Halishahar</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>Six</t>
+          <t>Eight</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>3754</v>
+        <v>3753</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>63126057</t>
+          <t>63226075</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Admit_63126057</t>
+          <t>Admit_63226075</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Ayman Muzdahir</t>
+          <t>Fatema Akter Samiya</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Md. Anisur Rahman</t>
+          <t>Mosaruf hossain</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Mirza Ahmed Ispahani High School</t>
+          <t>Silver Bells Kindergarten &amp; Girls' High School</t>
         </is>
       </c>
       <c r="H215" t="n">
@@ -12944,7 +12939,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>+8801722363929</t>
+          <t>+8801869336887</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -12965,16 +12960,16 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>3755</v>
+        <v>3754</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>71126049</t>
+          <t>63126057</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Admit_71126049</t>
+          <t>Admit_63126057</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -12984,171 +12979,171 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Urfat Doud Wasit</t>
+          <t>Ayman Muzdahir</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Main Uddin</t>
+          <t>Md. Anisur Rahman</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>St. Xavier's School</t>
+          <t>Mirza Ahmed Ispahani High School</t>
         </is>
       </c>
       <c r="H216" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>+8801407471990</t>
+          <t>+8801722363929</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Halishahar</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Six</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3756</v>
+        <v>3755</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>82226047</t>
+          <t>71126049</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Admit_82226047</t>
+          <t>Admit_71126049</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Farabee Afreen</t>
+          <t>Urfat Doud Wasit</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Md Ashraf Faruky</t>
+          <t>Main Uddin</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Bangladesh Noubahini School and College, Chattogram</t>
+          <t>St. Xavier's School</t>
         </is>
       </c>
       <c r="H217" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>+8801644239778</t>
+          <t>+8801407471990</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Patenga</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>3757</v>
+        <v>3756</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>63126058</t>
+          <t>82226047</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Admit_63126058</t>
+          <t>Admit_82226047</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Nahin Al Hossain</t>
+          <t>Farabee Afreen</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Moinuddin Chowdhury</t>
+          <t>Md Ashraf Faruky</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Central public school and college</t>
+          <t>Bangladesh Noubahini School and College, Chattogram</t>
         </is>
       </c>
       <c r="H218" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>+8801625289956</t>
+          <t>+8801644239778</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Agrabad</t>
+          <t>Patenga</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3758</v>
+        <v>3757</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>81126048</t>
+          <t>63126058</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Admit_81126048</t>
+          <t>Admit_63126058</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -13158,113 +13153,113 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Mohammad Tasnim Bin Imam</t>
+          <t>Nahin Al Hossain</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mohammad Imam Hossain</t>
+          <t>Moinuddin Chowdhury</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Ispahani Public School and College</t>
+          <t>Central public school and college</t>
         </is>
       </c>
       <c r="H219" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>+8801737860220</t>
+          <t>+8801625289956</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Agrabad</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3759</v>
+        <v>3758</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>53226122</t>
+          <t>81126048</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Admit_53226122</t>
+          <t>Admit_81126048</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>MARIAH MUBASSHIRA</t>
+          <t>Mohammad Tasnim Bin Imam</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>MOSHARROF HOSSAIN</t>
+          <t>Mohammad Imam Hossain</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>TICKET PRINTING PRESS COLONY GOVERNMENT PRIMARY SCHOOL</t>
+          <t>Ispahani Public School and College</t>
         </is>
       </c>
       <c r="H220" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>+8801817789767</t>
+          <t>+8801737860220</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Halishahar</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>3760</v>
+        <v>3759</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>61226057</t>
+          <t>53226122</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Admit_61226057</t>
+          <t>Admit_53226122</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -13274,75 +13269,75 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Humaira Chowdhury Shabiha</t>
+          <t>MARIAH MUBASSHIRA</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Mohammad Zahedul Islam Chowdhury</t>
+          <t>MOSHARROF HOSSAIN</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Al Hera Ideal Madrasha</t>
+          <t>TICKET PRINTING PRESS COLONY GOVERNMENT PRIMARY SCHOOL</t>
         </is>
       </c>
       <c r="H221" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>+8801880400184</t>
+          <t>+8801817789767</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Halishahar</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>Six</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>3761</v>
+        <v>3760</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>63126059</t>
+          <t>61226057</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Admit_63126059</t>
+          <t>Admit_61226057</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Arian Ibne Alam</t>
+          <t>Humaira Chowdhury Shabiha</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Khorshed Alam</t>
+          <t>Mohammad Zahedul Islam Chowdhury</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Halishahar Cantonment Public School And College</t>
+          <t>Al Hera Ideal Madrasha</t>
         </is>
       </c>
       <c r="H222" t="n">
@@ -13350,37 +13345,37 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>+8801316360975</t>
+          <t>+8801880400184</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Halishahar</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Six</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3762</v>
+        <v>3761</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>73126048</t>
+          <t>63126059</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Admit_73126048</t>
+          <t>Admit_63126059</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -13390,25 +13385,25 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>RIDWAN HASSAN RAZ</t>
+          <t>Arian Ibne Alam</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>MAHADE HASSAN</t>
+          <t>Khorshed Alam</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Halishahar cantonment public school and college</t>
+          <t>Halishahar Cantonment Public School And College</t>
         </is>
       </c>
       <c r="H223" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>+8801628267333</t>
+          <t>+8801316360975</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -13423,22 +13418,22 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>SEVEN , EV</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>3763</v>
+        <v>3762</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>63126060</t>
+          <t>73126048</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Admit_63126060</t>
+          <t>Admit_73126048</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -13448,25 +13443,25 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>SREYAN BARUA</t>
+          <t>RIDWAN HASSAN RAZ</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>EMON BARUA</t>
+          <t>MAHADE HASSAN</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Halishahar Cantonment Public School &amp; College</t>
+          <t>Halishahar cantonment public school and college</t>
         </is>
       </c>
       <c r="H224" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>+8801816244865</t>
+          <t>+8801628267333</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -13481,50 +13476,50 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>Six</t>
+          <t>SEVEN , EV</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>3764</v>
+        <v>3763</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>73226062</t>
+          <t>63126060</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Admit_73226062</t>
+          <t>Admit_63126060</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>AYSHA ARABI TALUKDAR</t>
+          <t>SREYAN BARUA</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>RASHEDUL HASAN TALUKDAR</t>
+          <t>EMON BARUA</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Bangladesh Mohila Samiti Girls High School and College</t>
+          <t>Halishahar Cantonment Public School &amp; College</t>
         </is>
       </c>
       <c r="H225" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>+8801885211732</t>
+          <t>+8801816244865</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -13539,22 +13534,22 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Six</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>3765</v>
+        <v>3764</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>73226063</t>
+          <t>73226062</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Admit_73226063</t>
+          <t>Admit_73226062</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -13564,17 +13559,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>MIFTAHUL JANNAT NOWRIN</t>
+          <t>AYSHA ARABI TALUKDAR</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>ALI AHMED HOWLADER</t>
+          <t>RASHEDUL HASAN TALUKDAR</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Bandar Mohammadia Dakhil Madrasah</t>
+          <t>Bangladesh Mohila Samiti Girls High School and College</t>
         </is>
       </c>
       <c r="H226" t="n">
@@ -13582,7 +13577,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>+8801888760892</t>
+          <t>+8801885211732</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -13603,16 +13598,16 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>3766</v>
+        <v>3765</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>91226018</t>
+          <t>73226063</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Admit_91226018</t>
+          <t>Admit_73226063</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -13622,83 +13617,83 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Aunkita Dhar Purna</t>
+          <t>MIFTAHUL JANNAT NOWRIN</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mukul Kanti Dhar</t>
+          <t>ALI AHMED HOWLADER</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Ispahani Public School and College</t>
+          <t>Bandar Mohammadia Dakhil Madrasah</t>
         </is>
       </c>
       <c r="H227" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>+8801973632669</t>
+          <t>+8801888760892</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Halishahar</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>Nine</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>3768</v>
+        <v>3766</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>51126055</t>
+          <t>91226018</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Admit_51126055</t>
+          <t>Admit_91226018</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Md.Rohan Adnana Arik</t>
+          <t>Aunkita Dhar Purna</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Md.Delowar Hossain</t>
+          <t>Mukul Kanti Dhar</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Gashful Paran Rahman School</t>
+          <t>Ispahani Public School and College</t>
         </is>
       </c>
       <c r="H228" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>+8801818100017</t>
+          <t>+8801973632669</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -13713,32 +13708,32 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>5 (Five)</t>
+          <t>Nine</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>3769</v>
+        <v>3768</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>71226063</t>
+          <t>51126055</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Admit_71226063</t>
+          <t>Admit_51126055</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Jun An Nur Zara</t>
+          <t>Md.Rohan Adnana Arik</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -13748,11 +13743,11 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Aparnacharan City Corporation girls high school and college</t>
+          <t>Gashful Paran Rahman School</t>
         </is>
       </c>
       <c r="H229" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
@@ -13771,22 +13766,22 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>7 (Saven)</t>
+          <t>5 (Five)</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>3770</v>
+        <v>3769</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>41226061</t>
+          <t>71226063</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Admit_41226061</t>
+          <t>Admit_71226063</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -13796,25 +13791,25 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Fairuz sara</t>
+          <t>Jun An Nur Zara</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>মোহাম্মদ রেজাউল করিম</t>
+          <t>Md.Delowar Hossain</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>রেলওয়ে পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>Aparnacharan City Corporation girls high school and college</t>
         </is>
       </c>
       <c r="H230" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>+8801722289291</t>
+          <t>+8801818100017</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -13829,22 +13824,22 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>৪থ</t>
+          <t>7 (Saven)</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>3772</v>
+        <v>3770</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>12226012</t>
+          <t>41226061</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Admit_12226012</t>
+          <t>Admit_41226061</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -13854,113 +13849,113 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Israt Jahan</t>
+          <t>Fairuz sara</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Mohammed Jafor Iqbal Talukder</t>
+          <t>মোহাম্মদ রেজাউল করিম</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>TSP Complex Secondary School</t>
+          <t>রেলওয়ে পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="H231" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>+8801839149388</t>
+          <t>+8801722289291</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Patenga</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>৪থ</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>3773</v>
+        <v>3772</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>71126050</t>
+          <t>12226012</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Admit_71126050</t>
+          <t>Admit_12226012</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Mohammed Fahimur Rahman</t>
+          <t>Israt Jahan</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>মোহাম্মদ রেজাউল করিম</t>
+          <t>Mohammed Jafor Iqbal Talukder</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>সেন্ট্রাল পাবলিক স্কুল এন্ড কলেজ</t>
+          <t>TSP Complex Secondary School</t>
         </is>
       </c>
       <c r="H232" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>+8801722289291</t>
+          <t>+8801839149388</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Patenga</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>৭ম</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>3774</v>
+        <v>3773</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>71126051</t>
+          <t>71126050</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Admit_71126051</t>
+          <t>Admit_71126050</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -13970,17 +13965,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>MD.Montasirul Hoque</t>
+          <t>Mohammed Fahimur Rahman</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Mohammed Monsurul Hoque</t>
+          <t>মোহাম্মদ রেজাউল করিম</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Chattogram Collegiate school</t>
+          <t>সেন্ট্রাল পাবলিক স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="H233" t="n">
@@ -13988,7 +13983,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>+8801815569474</t>
+          <t>+8801722289291</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -14003,22 +13998,22 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>৭ম</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>3775</v>
+        <v>3774</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>51126056</t>
+          <t>71126051</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Admit_51126056</t>
+          <t>Admit_71126051</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -14028,25 +14023,25 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Taskinul Tahkik Afif</t>
+          <t>MD.Montasirul Hoque</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Shamsul Alam</t>
+          <t>Mohammed Monsurul Hoque</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Ispahani Public School &amp; College</t>
+          <t>Chattogram Collegiate school</t>
         </is>
       </c>
       <c r="H234" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>+8801921375492</t>
+          <t>+8801815569474</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -14061,50 +14056,50 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>3776</v>
+        <v>3775</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>81226032</t>
+          <t>51126056</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Admit_81226032</t>
+          <t>Admit_51126056</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Rehan Samanta</t>
+          <t>Taskinul Tahkik Afif</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Md Ariful Islam</t>
+          <t>Shamsul Alam</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Dr.Khastagir Govt. Girls' High School</t>
+          <t>Ispahani Public School &amp; College</t>
         </is>
       </c>
       <c r="H235" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>+8801714226416</t>
+          <t>+8801921375492</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -14119,90 +14114,90 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>Class Eight</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>3777</v>
+        <v>3776</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>93126019</t>
+          <t>81226032</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Admit_93126019</t>
+          <t>Admit_81226032</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Jawad alhisham</t>
+          <t>Rehan Samanta</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Rokan Uddin sikder</t>
+          <t>Md Ariful Islam</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Chattogram port authority high school</t>
+          <t>Dr.Khastagir Govt. Girls' High School</t>
         </is>
       </c>
       <c r="H236" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>+8801815118150</t>
+          <t>+8801714226416</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Halishahar</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Class Eight</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>3778</v>
+        <v>3777</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>83226052</t>
+          <t>93126019</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Admit_83226052</t>
+          <t>Admit_93126019</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Mariam maliha</t>
+          <t>Jawad alhisham</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -14212,15 +14207,15 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Chattogram port Authority girls high school</t>
+          <t>Chattogram port authority high school</t>
         </is>
       </c>
       <c r="H237" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>+8801835459699</t>
+          <t>+8801815118150</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -14235,42 +14230,42 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>3779</v>
+        <v>3778</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>81126049</t>
+          <t>83226052</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Admit_81126049</t>
+          <t>Admit_83226052</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Hasnainul Karim</t>
+          <t>Mariam maliha</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>MD Razaul razaul Karim</t>
+          <t>Rokan Uddin sikder</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Government Muslim High school</t>
+          <t>Chattogram port Authority girls high school</t>
         </is>
       </c>
       <c r="H238" t="n">
@@ -14278,17 +14273,17 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>+8801870747189</t>
+          <t>+8801835459699</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Halishahar</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -14299,36 +14294,36 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>3780</v>
+        <v>3779</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>83226053</t>
+          <t>81126049</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Admit_83226053</t>
+          <t>Admit_81126049</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Tasnia Morshed Noshin</t>
+          <t>Hasnainul Karim</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Md. Mursed</t>
+          <t>MD Razaul razaul Karim</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Halishahar Cantonment Public School and College</t>
+          <t>Government Muslim High school</t>
         </is>
       </c>
       <c r="H239" t="n">
@@ -14336,17 +14331,17 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>+8801857536736</t>
+          <t>+8801870747189</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Halishahar</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -14357,74 +14352,74 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>3781</v>
+        <v>3780</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>91126012</t>
+          <t>83226053</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Admit_91126012</t>
+          <t>Admit_83226053</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Efnehan Adnan Rafi</t>
+          <t>Tasnia Morshed Noshin</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Rabiul Hossen Arman</t>
+          <t>Md. Mursed</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Railway Public High School</t>
+          <t>Halishahar Cantonment Public School and College</t>
         </is>
       </c>
       <c r="H240" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>+8801886185628</t>
+          <t>+8801857536736</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Halishahar</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>Nine</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>3783</v>
+        <v>3781</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>61126053</t>
+          <t>91126012</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Admit_61126053</t>
+          <t>Admit_91126012</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -14434,25 +14429,25 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Mohammad Imtiaz Uddin</t>
+          <t>Efnehan Adnan Rafi</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Md.Emam Uddin</t>
+          <t>Rabiul Hossen Arman</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Ar -Risala Madrasa</t>
+          <t>Railway Public High School</t>
         </is>
       </c>
       <c r="H241" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>+8801890805009</t>
+          <t>+8801886185628</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -14467,22 +14462,22 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>Six</t>
+          <t>Nine</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>3787</v>
+        <v>3783</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>73126049</t>
+          <t>61126053</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Admit_73126049</t>
+          <t>Admit_61126053</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -14492,83 +14487,78 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Hrishov Dey</t>
+          <t>Mohammad Imtiaz Uddin</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Amit Dey</t>
+          <t>Md.Emam Uddin</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Nashirabad Govt.High School.Chattogram.</t>
+          <t>Ar -Risala Madrasa</t>
         </is>
       </c>
       <c r="H242" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>+8801857647442</t>
+          <t>+8801890805009</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Agrabad</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>Seven, (7)</t>
+          <t>Six</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>3788</v>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>43126084</t>
-        </is>
+        <v>3786</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Admit_43126084</t>
+          <t>Admit_3786</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Mohammad Ashaz Bhuiyan</t>
+          <t>Humaira Jahan Rejum</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Abul Kashem Bhuiyan</t>
+          <t>MD Shahjahan</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Halishahar Cantonment Public School and College</t>
+          <t>Kattali Ideal Kinder Garten And High School</t>
         </is>
       </c>
       <c r="H243" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>+8801759381811</t>
+          <t>+8801815511550</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -14578,85 +14568,85 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>Four</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>3790</v>
+        <v>3787</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>41226062</t>
+          <t>73126049</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Admit_41226062</t>
+          <t>Admit_73126049</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Rumaisa Islam Chowdhury</t>
+          <t>Hrishov Dey</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Raisul Islam Chowdhury</t>
+          <t>Amit Dey</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Leader's school &amp; College Chattogram</t>
+          <t>Nashirabad Govt.High School.Chattogram.</t>
         </is>
       </c>
       <c r="H244" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>+8801674784837</t>
+          <t>+8801857647442</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Agrabad</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>Seven, (7)</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>3791</v>
+        <v>3788</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>42126051</t>
+          <t>43126084</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Admit_42126051</t>
+          <t>Admit_43126084</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -14666,17 +14656,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Tuhin Ahmed</t>
+          <t>Mohammad Ashaz Bhuiyan</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Dulal Ahmed</t>
+          <t>Abul Kashem Bhuiyan</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Maizpara Madrasha Patenga</t>
+          <t>Halishahar Cantonment Public School and College</t>
         </is>
       </c>
       <c r="H245" t="n">
@@ -14684,95 +14674,95 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>+8801914360214</t>
+          <t>+8801759381811</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Patenga</t>
+          <t>Halishahar</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>Four</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>3792</v>
+        <v>3790</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>82126036</t>
+          <t>41226062</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Admit_82126036</t>
+          <t>Admit_41226062</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Tasin Ahmed</t>
+          <t>Rumaisa Islam Chowdhury</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Dulal Ahmed</t>
+          <t>Raisul Islam Chowdhury</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Maizpara Madrasha Patenga</t>
+          <t>Leader's school &amp; College Chattogram</t>
         </is>
       </c>
       <c r="H246" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>+8801914360214</t>
+          <t>+8801674784837</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Patenga</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>3793</v>
+        <v>3791</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>51126057</t>
+          <t>42126051</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Admit_51126057</t>
+          <t>Admit_42126051</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -14782,55 +14772,55 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Wahiyan Ibtisam Towaha</t>
+          <t>Tuhin Ahmed</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Mohammad Omar Faruque</t>
+          <t>Dulal Ahmed</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Al-Zaber Institute</t>
+          <t>Maizpara Madrasha Patenga</t>
         </is>
       </c>
       <c r="H247" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>+8801675710977</t>
+          <t>+8801914360214</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Patenga</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>3794</v>
+        <v>3792</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>82126037</t>
+          <t>82126036</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Admit_82126037</t>
+          <t>Admit_82126036</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -14840,17 +14830,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Ferdous Khaled Ramim</t>
+          <t>Tasin Ahmed</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Asmaul Alam</t>
+          <t>Dulal Ahmed</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Child Cyme Academy</t>
+          <t>Maizpara Madrasha Patenga</t>
         </is>
       </c>
       <c r="H248" t="n">
@@ -14858,7 +14848,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>+8801919610661</t>
+          <t>+8801914360214</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -14879,44 +14869,44 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>3795</v>
+        <v>3793</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>41226063</t>
+          <t>51126057</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Admit_41226063</t>
+          <t>Admit_51126057</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Miskatul Jannat Labiba</t>
+          <t>Wahiyan Ibtisam Towaha</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Md. Jahirul Islam</t>
+          <t>Mohammad Omar Faruque</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Baitus Shraf Adarsha Kamil Madrasha</t>
+          <t>Al-Zaber Institute</t>
         </is>
       </c>
       <c r="H249" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>+8801816237099</t>
+          <t>+8801675710977</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -14931,22 +14921,22 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>Four</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>3796</v>
+        <v>3794</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>71126052</t>
+          <t>82126037</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Admit_71126052</t>
+          <t>Admit_82126037</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -14956,83 +14946,83 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>MOHAMMAD NABHAN IQBAL</t>
+          <t>Ferdous Khaled Ramim</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নওশাদ ইকবাল</t>
+          <t>Asmaul Alam</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
+          <t>Child Cyme Academy</t>
         </is>
       </c>
       <c r="H250" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>+8801817750764</t>
+          <t>+8801919610661</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Patenga</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>সপ্তম,( ৭ম )</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>3797</v>
+        <v>3795</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>51126058</t>
+          <t>41226063</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Admit_51126058</t>
+          <t>Admit_41226063</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>MOHAMMAD NUBAID IQBAL</t>
+          <t>Miskatul Jannat Labiba</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>মোহাম্মদ নওশাদ ইকবাল</t>
+          <t>Md. Jahirul Islam</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
+          <t>Baitus Shraf Adarsha Kamil Madrasha</t>
         </is>
       </c>
       <c r="H251" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>+8801817750764</t>
+          <t>+8801816237099</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -15047,138 +15037,138 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>পঞ্চম (৫ম)</t>
+          <t>Four</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>3799</v>
+        <v>3796</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>93226043</t>
+          <t>71126052</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Admit_93226043</t>
+          <t>Admit_71126052</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Taslima Mim Nura</t>
+          <t>MOHAMMAD NABHAN IQBAL</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Md. Anamul Hoque</t>
+          <t>মোহাম্মদ নওশাদ ইকবাল</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Soraipara city corporation high school</t>
+          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
         </is>
       </c>
       <c r="H252" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>+8801814381041</t>
+          <t>+8801817750764</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Halishahar</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>সপ্তম,( ৭ম )</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>3820</v>
+        <v>3797</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>83226054</t>
+          <t>51126058</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Admit_83226054</t>
+          <t>Admit_51126058</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Faiza Kowsary</t>
+          <t>MOHAMMAD NUBAID IQBAL</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Abul Khair</t>
+          <t>মোহাম্মদ নওশাদ ইকবাল</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Mirza Ahmed Ishpahani High School</t>
+          <t>ইস্পাহানি পাবলিক স্কুল এন্ড কলেজ, চট্টগ্রাম।</t>
         </is>
       </c>
       <c r="H253" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>+8801819671754</t>
+          <t>+8801817750764</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Halishahar</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>Class 8</t>
+          <t>পঞ্চম (৫ম)</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>3821</v>
+        <v>3799</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>41226064</t>
+          <t>93226043</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Admit_41226064</t>
+          <t>Admit_93226043</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -15188,133 +15178,133 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Kazi Noushin Fatema</t>
+          <t>Taslima Mim Nura</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Kazi Masudul Karim</t>
+          <t>Md. Anamul Hoque</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>AUNKUR SOCIETY GIRLS' HIGH SCHOOL</t>
+          <t>Soraipara city corporation high school</t>
         </is>
       </c>
       <c r="H254" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>+8801871585495</t>
+          <t>+8801814381041</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Halishahar</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>3822</v>
+        <v>3820</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>91126013</t>
+          <t>83226054</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Admit_91126013</t>
+          <t>Admit_83226054</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>MD.Jubayed Hossain</t>
+          <t>Faiza Kowsary</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Kobir Ahammed</t>
+          <t>Abul Khair</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Orbit residential school and College</t>
+          <t>Mirza Ahmed Ishpahani High School</t>
         </is>
       </c>
       <c r="H255" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>+8801887000492</t>
+          <t>+8801819671754</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Halishahar</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>Nine</t>
+          <t>Class 8</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>3823</v>
+        <v>3821</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>41126046</t>
+          <t>41226064</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Admit_41126046</t>
+          <t>Admit_41226064</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Md Adnan Bhuiyan</t>
+          <t>Kazi Noushin Fatema</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Md Asfak Uddin Dulal</t>
+          <t>Kazi Masudul Karim</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>CMP School &amp; College</t>
+          <t>AUNKUR SOCIETY GIRLS' HIGH SCHOOL</t>
         </is>
       </c>
       <c r="H256" t="n">
@@ -15322,7 +15312,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>+8801852784696</t>
+          <t>+8801871585495</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -15343,16 +15333,16 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>3825</v>
+        <v>3822</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>43126085</t>
+          <t>91126013</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Admit_43126085</t>
+          <t>Admit_91126013</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -15362,55 +15352,55 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Ariyan Das Shawon</t>
+          <t>MD.Jubayed Hossain</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Joydev Chandra Das</t>
+          <t>Kobir Ahammed</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Ispahani Public School &amp; College</t>
+          <t>Orbit residential school and College</t>
         </is>
       </c>
       <c r="H257" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>+8801849375354</t>
+          <t>+8801887000492</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Agrabad</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>Four</t>
+          <t>Nine</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>3826</v>
+        <v>3823</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>43126086</t>
+          <t>41126046</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Admit_43126086</t>
+          <t>Admit_41126046</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -15420,17 +15410,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Wriddhiman Das-</t>
+          <t>Md Adnan Bhuiyan</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Jishu Kumar Das</t>
+          <t>Md Asfak Uddin Dulal</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Ispahani Public School And College Chattogram</t>
+          <t>CMP School &amp; College</t>
         </is>
       </c>
       <c r="H258" t="n">
@@ -15438,17 +15428,17 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>+8801818024461</t>
+          <t>+8801852784696</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Agrabad</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -15459,74 +15449,74 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>3830</v>
+        <v>3825</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>71226064</t>
+          <t>43126085</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Admit_71226064</t>
+          <t>Admit_43126085</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Sadeka sultana Espa</t>
+          <t>Ariyan Das Shawon</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Shahadat hossen</t>
+          <t>Joydev Chandra Das</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>CMP School and college</t>
+          <t>Ispahani Public School &amp; College</t>
         </is>
       </c>
       <c r="H259" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>+8801889254339</t>
+          <t>+8801849375354</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Agrabad</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Four</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>3831</v>
+        <v>3826</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>51126059</t>
+          <t>43126086</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Admit_51126059</t>
+          <t>Admit_43126086</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -15536,83 +15526,83 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Shoyaib hossen shihab</t>
+          <t>Wriddhiman Das-</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Shahadat hossen</t>
+          <t>Jishu Kumar Das</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>CMP School and college</t>
+          <t>Ispahani Public School And College Chattogram</t>
         </is>
       </c>
       <c r="H260" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>+8801889254339</t>
+          <t>+8801818024461</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Agrabad</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>3832</v>
+        <v>3830</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>41126047</t>
+          <t>71226064</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Admit_41126047</t>
+          <t>Admit_71226064</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Aronno Barua (Arko)</t>
+          <t>Sadeka sultana Espa</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>RAJIB BARUA</t>
+          <t>Shahadat hossen</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>ISPAHANI SCHOOL AND COLLEGE</t>
+          <t>CMP School and college</t>
         </is>
       </c>
       <c r="H261" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>+8801850735885</t>
+          <t>+8801889254339</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -15627,22 +15617,22 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>3833</v>
+        <v>3831</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>53126068</t>
+          <t>51126059</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Admit_53126068</t>
+          <t>Admit_51126059</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -15652,17 +15642,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Arka Deep Barua</t>
+          <t>Shoyaib hossen shihab</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Sidul Barua</t>
+          <t>Shahadat hossen</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Chattogram Callegiat school</t>
+          <t>CMP School and college</t>
         </is>
       </c>
       <c r="H262" t="n">
@@ -15670,17 +15660,17 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>+8801860706868</t>
+          <t>+8801889254339</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Agrabad</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -15691,16 +15681,16 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>3835</v>
+        <v>3832</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>71126053</t>
+          <t>41126047</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Admit_71126053</t>
+          <t>Admit_41126047</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -15710,25 +15700,25 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Akm Ahnaf hasan</t>
+          <t>Aronno Barua (Arko)</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>মো ইউসুফ</t>
+          <t>RAJIB BARUA</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>সি এম পি স্কুল এন্ড কলেজ</t>
+          <t>ISPAHANI SCHOOL AND COLLEGE</t>
         </is>
       </c>
       <c r="H263" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>+8801837287515</t>
+          <t>+8801850735885</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -15743,108 +15733,103 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>সেভেন</t>
+          <t>FOUR</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>3836</v>
+        <v>3833</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>71226065</t>
+          <t>53126068</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Admit_71226065</t>
+          <t>Admit_53126068</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Sarina Sabria Adifa</t>
+          <t>Arka Deep Barua</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Muhammad Abu Musa Al- Amin</t>
+          <t>Sidul Barua</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Alhaj Yakub Ali Girls High school and College</t>
+          <t>Chattogram Callegiat school</t>
         </is>
       </c>
       <c r="H264" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>+8801812527014</t>
+          <t>+8801860706868</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Agrabad</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>Seven</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>3837</v>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>53126069</t>
-        </is>
+        <v>3834</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Admit_53126069</t>
+          <t>Admit_3834</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Ahmad Ibne Naser</t>
+          <t>Faria Jamal</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Mohammad Abu Naser</t>
+          <t>MD Jamal Uddin</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Sabujchaiya Biddanikatan</t>
+          <t>Feni Govt Girls High School</t>
         </is>
       </c>
       <c r="H265" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>+8801913853290</t>
+          <t>+8801820293583</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -15854,55 +15839,55 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>Five</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>3838</v>
+        <v>3835</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>51226070</t>
+          <t>71126053</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Admit_51226070</t>
+          <t>Admit_71126053</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Suhaira Marium Ariba</t>
+          <t>Akm Ahnaf hasan</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Muhammad Abu Musa Al-Amin</t>
+          <t>মো ইউসুফ</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Alhaj Yakub Ali Girls High school and College</t>
+          <t>সি এম পি স্কুল এন্ড কলেজ</t>
         </is>
       </c>
       <c r="H266" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>+8801812527014</t>
+          <t>+8801837287515</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -15917,22 +15902,22 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>Five</t>
+          <t>সেভেন</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>3839</v>
+        <v>3836</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>71226066</t>
+          <t>71226065</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Admit_71226066</t>
+          <t>Admit_71226065</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -15942,17 +15927,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Ansha Nurain</t>
+          <t>Sarina Sabria Adifa</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Jahangir Alam</t>
+          <t>Muhammad Abu Musa Al- Amin</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Talimun Nisa Madrasah, Mia Khan Nagar, Bakalia,Ctg</t>
+          <t>Alhaj Yakub Ali Girls High school and College</t>
         </is>
       </c>
       <c r="H267" t="n">
@@ -15960,7 +15945,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>+8801818671992</t>
+          <t>+8801812527014</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -15975,55 +15960,55 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>Seven</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>3840</v>
+        <v>3837</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>63226076</t>
+          <t>53126069</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Admit_63226076</t>
+          <t>Admit_53126069</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Hamim sizda nawsin</t>
+          <t>Ahmad Ibne Naser</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>শাহা জাহান</t>
+          <t>Mohammad Abu Naser</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>বাকলিয়া আদর্শ বালিকা উচ্চ বিদ্যালয়</t>
+          <t>Sabujchaiya Biddanikatan</t>
         </is>
       </c>
       <c r="H268" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>+8801816162240</t>
+          <t>+8801913853290</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Agrabad</t>
+          <t>Halishahar</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -16033,22 +16018,22 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>Five</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>3841</v>
+        <v>3838</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>71226067</t>
+          <t>51226070</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Admit_71226067</t>
+          <t>Admit_51226070</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -16058,25 +16043,25 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Jannatul Mushfika</t>
+          <t>Suhaira Marium Ariba</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Md Abdul mannan vhyain</t>
+          <t>Muhammad Abu Musa Al-Amin</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>St marys school</t>
+          <t>Alhaj Yakub Ali Girls High school and College</t>
         </is>
       </c>
       <c r="H269" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>+8801822613125</t>
+          <t>+8801812527014</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -16091,22 +16076,22 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Five</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>3842</v>
+        <v>3839</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>12226013</t>
+          <t>71226066</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Admit_12226013</t>
+          <t>Admit_71226066</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -16116,151 +16101,146 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Miftahul jannat</t>
+          <t>Ansha Nurain</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>MD Nasir Uddin</t>
+          <t>Jahangir Alam</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>TSP Complex Secondary School</t>
+          <t>Talimun Nisa Madrasah, Mia Khan Nagar, Bakalia,Ctg</t>
         </is>
       </c>
       <c r="H270" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>+8801859372985</t>
+          <t>+8801818671992</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Patenga</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>Ten</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
-        <v>3843</v>
-      </c>
-      <c r="B271" s="2" t="inlineStr">
-        <is>
-          <t>41126040</t>
-        </is>
-      </c>
-      <c r="C271" s="2" t="inlineStr">
-        <is>
-          <t>Admit_41126040_Duplicate</t>
-        </is>
-      </c>
-      <c r="D271" s="2" t="inlineStr">
-        <is>
-          <t>Boy</t>
-        </is>
-      </c>
-      <c r="E271" s="2" t="inlineStr">
-        <is>
-          <t>Safwan Zaman Ahnaf</t>
-        </is>
-      </c>
-      <c r="F271" s="2" t="inlineStr">
-        <is>
-          <t>Md Shahiduzzaman</t>
-        </is>
-      </c>
-      <c r="G271" s="2" t="inlineStr">
-        <is>
-          <t>Delta School and College</t>
-        </is>
-      </c>
-      <c r="H271" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I271" s="2" t="inlineStr">
-        <is>
-          <t>+8801850401816</t>
-        </is>
-      </c>
-      <c r="J271" s="2" t="inlineStr">
-        <is>
-          <t>Dewanhat</t>
-        </is>
-      </c>
-      <c r="K271" s="2" t="inlineStr">
-        <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
-        </is>
-      </c>
-      <c r="L271" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M271" s="2" t="inlineStr">
-        <is>
-          <t>Duplicate of order 3561 (same name &amp; father, different mobile)</t>
+      <c r="A271" t="n">
+        <v>3840</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>63226076</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Admit_63226076</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Hamim sizda nawsin</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>শাহা জাহান</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>বাকলিয়া আদর্শ বালিকা উচ্চ বিদ্যালয়</t>
+        </is>
+      </c>
+      <c r="H271" t="n">
+        <v>6</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>+8801816162240</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>Agrabad</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>সিলভার বেলস কিন্ডারগার্টেন এন্ড গার্লস হাই স্কুল</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>3844</v>
+        <v>3841</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>81126057</t>
+          <t>71226067</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Admit_81126057</t>
+          <t>Admit_71226067</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Twasin Alam</t>
+          <t>Jannatul Mushfika</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Md. Khurshidul Alam</t>
+          <t>Md Abdul mannan vhyain</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Chattogram Collegiate School</t>
+          <t>St marys school</t>
         </is>
       </c>
       <c r="H272" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>+8801815287418</t>
+          <t>+8801822613125</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>Halishahar</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -16270,196 +16250,201 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>3846</v>
+        <v>3842</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>71126059</t>
+          <t>12226013</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Admit_71126059</t>
+          <t>Admit_12226013</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Miftahul jannat</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>MD Nasir Uddin</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>TSP Complex Secondary School</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>10</v>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>+8801859372985</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>Patenga</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Ten</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>3843</v>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>41126040</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>Admit_41126040_Duplicate</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
           <t>Boy</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>Md.Ridowan Bin Arif</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>Md.Ariful Islam</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>Chattogram Collegiate School</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
-        <v>7</v>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>+8801722966006</t>
-        </is>
-      </c>
-      <c r="J273" t="inlineStr">
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>Safwan Zaman Ahnaf</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>Md Shahiduzzaman</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>Delta School and College</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>+8801850401816</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr">
         <is>
           <t>Dewanhat</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr">
+      <c r="K274" s="2" t="inlineStr">
         <is>
           <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr">
-        <is>
-          <t>Seven</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="n">
-        <v>3847</v>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>51126067</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Admit_51126067</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>Boy</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>AHMAD JAHEE</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>JALAL UDDIN</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>CHATTOGRAM COLLEGIATE SCHOOL</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
-        <v>5</v>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>+8801626914730</t>
-        </is>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>Dewanhat</t>
-        </is>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
-        </is>
-      </c>
-      <c r="L274" t="inlineStr">
-        <is>
-          <t>FIVE</t>
+      <c r="L274" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M274" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate of order 3561 (same name &amp; father, different mobile)</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>3848</v>
+        <v>3844</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>72226069</t>
+          <t>81126057</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Admit_72226069</t>
+          <t>Admit_81126057</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Nusrat Jahan</t>
+          <t>Twasin Alam</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Mohammed Jafor Iqbal Talukder</t>
+          <t>Md. Khurshidul Alam</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>CDDL Navy School</t>
+          <t>Chattogram Collegiate School</t>
         </is>
       </c>
       <c r="H275" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>+8801336826867</t>
+          <t>+8801815287418</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Patenga</t>
+          <t>Halishahar</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>3849</v>
+        <v>3846</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>91126020</t>
+          <t>71126059</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Admit_91126020</t>
+          <t>Admit_71126059</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -16469,30 +16454,30 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Md.Samiul Islam Alvi</t>
+          <t>Md.Ridowan Bin Arif</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Md Saiful Islam</t>
+          <t>Md.Ariful Islam</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Ispahani Public School And College</t>
+          <t>Chattogram Collegiate School</t>
         </is>
       </c>
       <c r="H276" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>+8801717944271</t>
+          <t>+8801722966006</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Agrabad</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -16502,50 +16487,50 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>Seven</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>3850</v>
+        <v>3847</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>61226065</t>
+          <t>51126067</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Admit_61226065</t>
+          <t>Admit_51126067</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Tasnia Farin Yusha</t>
+          <t>AHMAD JAHEE</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Mohammad Mojibul Hoque</t>
+          <t>JALAL UDDIN</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Dr. Khastagir Govt. Girls High School</t>
+          <t>CHATTOGRAM COLLEGIATE SCHOOL</t>
         </is>
       </c>
       <c r="H277" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>+8801970433883</t>
+          <t>+8801626914730</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
@@ -16560,50 +16545,50 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>FIVE</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>3852</v>
+        <v>3848</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>62126074</t>
+          <t>72226069</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Admit_62126074</t>
+          <t>Admit_72226069</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Prantik Barua Dhrubo</t>
+          <t>Nusrat Jahan</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Dipak Barua</t>
+          <t>Mohammed Jafor Iqbal Talukder</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Green Bell School &amp; College</t>
+          <t>CDDL Navy School</t>
         </is>
       </c>
       <c r="H278" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>+8801612938480</t>
+          <t>+8801336826867</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -16618,22 +16603,22 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>Class Six</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>3853</v>
+        <v>3849</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>71126060</t>
+          <t>91126020</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Admit_71126060</t>
+          <t>Admit_91126020</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -16643,30 +16628,30 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>MD.Rayhan Alam</t>
+          <t>Md.Samiul Islam Alvi</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Jahangir Alam</t>
+          <t>Md Saiful Islam</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Chattogram Collegiate School, Chattogram</t>
+          <t>Ispahani Public School And College</t>
         </is>
       </c>
       <c r="H279" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>+8801851911435</t>
+          <t>+8801717944271</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Agrabad</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -16676,22 +16661,22 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>3854</v>
+        <v>3850</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>51226084</t>
+          <t>61226065</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Admit_51226084</t>
+          <t>Admit_61226065</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -16701,30 +16686,30 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Fahmida khanom alifa</t>
+          <t>Tasnia Farin Yusha</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Ayub khan</t>
+          <t>Mohammad Mojibul Hoque</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>South kattali pran hori model gov't primary school</t>
+          <t>Dr. Khastagir Govt. Girls High School</t>
         </is>
       </c>
       <c r="H280" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>+8801789865054</t>
+          <t>+8801970433883</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Halishahar</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -16734,22 +16719,22 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>Five</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>3856</v>
+        <v>3852</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>71126061</t>
+          <t>62126074</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Admit_71126061</t>
+          <t>Admit_62126074</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -16759,88 +16744,88 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Mosaidul Hossain Nihad</t>
+          <t>Prantik Barua Dhrubo</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Moazzam Hossain Molla</t>
+          <t>Dipak Barua</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Halishahar Cantonment Public School and College</t>
+          <t>Green Bell School &amp; College</t>
         </is>
       </c>
       <c r="H281" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>+8801675271093</t>
+          <t>+8801612938480</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Halishahar</t>
+          <t>Patenga</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>Seven</t>
+          <t>Class Six</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>3857</v>
+        <v>3853</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>61226066</t>
+          <t>71126060</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Admit_61226066</t>
+          <t>Admit_71126060</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Junaira Farisha Islam</t>
+          <t>MD.Rayhan Alam</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Me.Manirul Islam</t>
+          <t>Jahangir Alam</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>HCPSC</t>
+          <t>Chattogram Collegiate School, Chattogram</t>
         </is>
       </c>
       <c r="H282" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>+8801838518567</t>
+          <t>+8801851911435</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Halishahar</t>
+          <t>Dewanhat</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -16850,50 +16835,50 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>Six</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>3858</v>
+        <v>3854</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>41126054</t>
+          <t>51226084</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Admit_41126054</t>
+          <t>Admit_51226084</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Boy</t>
+          <t>Girl</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Zain Riyasat Islam</t>
+          <t>Fahmida khanom alifa</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Md.Manirul Islam</t>
+          <t>Ayub khan</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>HCPSC</t>
+          <t>South kattali pran hori model gov't primary school</t>
         </is>
       </c>
       <c r="H283" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>+8801838518567</t>
+          <t>+8801789865054</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -16908,42 +16893,42 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>Four</t>
+          <t>Five</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>3860</v>
+        <v>3856</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>71226070</t>
+          <t>71126061</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Admit_71226070</t>
+          <t>Admit_71126061</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Girl</t>
+          <t>Boy</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Olin Atfa</t>
+          <t>Mosaidul Hossain Nihad</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>MD. YEASIN ARAFAT</t>
+          <t>Moazzam Hossain Molla</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>GUL-E-ZAR BEGUM CITY CORP MUSLIM GIRLS HIGH SCHOOL</t>
+          <t>Halishahar Cantonment Public School and College</t>
         </is>
       </c>
       <c r="H284" t="n">
@@ -16951,12 +16936,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>+8801866358979</t>
+          <t>+8801675271093</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>Dewanhat</t>
+          <t>Halishahar</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -16972,64 +16957,821 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
+        <v>3857</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>61226066</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Admit_61226066</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Junaira Farisha Islam</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Me.Manirul Islam</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>HCPSC</t>
+        </is>
+      </c>
+      <c r="H285" t="n">
+        <v>6</v>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>+8801838518567</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>Halishahar</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Six</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>3858</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>41126054</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Admit_41126054</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Zain Riyasat Islam</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Md.Manirul Islam</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>HCPSC</t>
+        </is>
+      </c>
+      <c r="H286" t="n">
+        <v>4</v>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>+8801838518567</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>Halishahar</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Four</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>3860</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>71226070</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Admit_71226070</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Olin Atfa</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>MD. YEASIN ARAFAT</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>GUL-E-ZAR BEGUM CITY CORP MUSLIM GIRLS HIGH SCHOOL</t>
+        </is>
+      </c>
+      <c r="H287" t="n">
+        <v>7</v>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>+8801866358979</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>Dewanhat</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Seven</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
         <v>3861</v>
       </c>
-      <c r="B285" t="inlineStr">
+      <c r="B288" t="inlineStr">
         <is>
           <t>51126068</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr">
+      <c r="C288" t="inlineStr">
         <is>
           <t>Admit_51126068</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr">
+      <c r="D288" t="inlineStr">
         <is>
           <t>Boy</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr">
+      <c r="E288" t="inlineStr">
         <is>
           <t>AFSAN NAZRUL AR-RAFI</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr">
+      <c r="F288" t="inlineStr">
         <is>
           <t>MD. NAZRUL ISLAM</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr">
+      <c r="G288" t="inlineStr">
         <is>
           <t>Ispahani Public School &amp; College</t>
         </is>
       </c>
-      <c r="H285" t="n">
+      <c r="H288" t="n">
         <v>5</v>
       </c>
-      <c r="I285" t="inlineStr">
+      <c r="I288" t="inlineStr">
         <is>
           <t>+8801953031941</t>
         </is>
       </c>
-      <c r="J285" t="inlineStr">
+      <c r="J288" t="inlineStr">
         <is>
           <t>Dewanhat</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr">
+      <c r="K288" t="inlineStr">
         <is>
           <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
         </is>
       </c>
-      <c r="L285" t="inlineStr">
+      <c r="L288" t="inlineStr">
         <is>
           <t>Five</t>
         </is>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>3862</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Admit_3862</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>MD. ATIQUL ALAM RAFI</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>RUMAN</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>PRAVATI MADDHYAMIK SHIKKHA NIKETON</t>
+        </is>
+      </c>
+      <c r="H289" t="n">
+        <v>5</v>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>+8801712386612</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>Halishahar</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>FIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>3863</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Admit_3863</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>TAHASAN KHONDOKAR</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>MD IMRAN</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>PRAVATI MADDHYAMIK SHIKKHA NIKETON</t>
+        </is>
+      </c>
+      <c r="H290" t="n">
+        <v>5</v>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>+8801866605785</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>Halishahar</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>FIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>3864</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Admit_3864</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Afra Anwar</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>MD. Anwar Hossain</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Dr. Khastagir Govt. Girls High School</t>
+        </is>
+      </c>
+      <c r="H291" t="n">
+        <v>5</v>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>+8801816611258</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>Dewanhat</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>5,</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>3865</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Admit_3865</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Nusaiba Tarnnum</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Ismail jabiullah</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Nasirabad gov. girls high school.</t>
+        </is>
+      </c>
+      <c r="H292" t="n">
+        <v>8</v>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>+8801755792267</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>Dewanhat</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>3866</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Admit_3866</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Samaira Muntaha Arha</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Shahadat Hossain</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Halishahar Cantonment public school and college</t>
+        </is>
+      </c>
+      <c r="H293" t="n">
+        <v>6</v>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>+8801678060130</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>Halishahar</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>3867</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Admit_3867</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Mohammed Ahrar Rahman</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Mohammed Khalilur Rahman</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Chattogram Collegiate school</t>
+        </is>
+      </c>
+      <c r="H294" t="n">
+        <v>6</v>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>+8801818022749</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>Halishahar</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>Six</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>3868</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Admit_3868</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Abdullah al farhan</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Ershad Hossain</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Shah wali ullah institute</t>
+        </is>
+      </c>
+      <c r="H295" t="n">
+        <v>7</v>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>+8801836232866</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>Dewanhat</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>Seven</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>3869</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Admit_3869</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Jannatul Ferdous</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>মো. সেলিম উদ্দিন</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>পূর্ব টাইগারপাস সরকারি প্রাথমিক বিদ্যালয়</t>
+        </is>
+      </c>
+      <c r="H296" t="n">
+        <v>4</v>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>+8801577707123</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>Dewanhat</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>3871</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Admit_3871</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Syed nafis fuad</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Syed Nazmul huda</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Halishar cantonment public school and college</t>
+        </is>
+      </c>
+      <c r="H297" t="n">
+        <v>7</v>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>+8801981666653</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>Dewanhat</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>3872</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Admit_3872</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Imran Al Noor</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Mohammed Noor Uddin</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>BN School and College</t>
+        </is>
+      </c>
+      <c r="H298" t="n">
+        <v>6</v>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>+8801742688898</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>Patenga</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>পতেঙ্গা উচ্চ বিদ্যালয়</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>3873</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Admit_3873</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Sabiha Kader Jahin</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>আব্দুল কাদের জিলানী</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>আলহাজ ইয়াকুব আলী স্কুল এন্ড কলেজ</t>
+        </is>
+      </c>
+      <c r="H299" t="n">
+        <v>6</v>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>+8801854312371</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>Halishahar</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>ষষ্ঠ শ্রেণি</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M285"/>
+  <autoFilter ref="A1:M299"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17203,7 +17945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18294,8 +19036,88 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>3869</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Fathers Name</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>মো. সেলিম উদ্দিন</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>written in Bangla (kept as entered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>3869</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Name of School</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>পূর্ব টাইগারপাস সরকারি প্রাথমিক বিদ্যালয়</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>written in Bangla (kept as entered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>3873</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Fathers Name</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>আব্দুল কাদের জিলানী</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>written in Bangla (kept as entered)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>3873</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Name of School</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>আলহাজ ইয়াকুব আলী স্কুল এন্ড কলেজ</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>written in Bangla (kept as entered)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D54"/>
+  <autoFilter ref="A1:D58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18343,7 +19165,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3">
@@ -18358,7 +19180,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4">
@@ -18388,7 +19210,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -18403,7 +19225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S286"/>
+  <dimension ref="A1:S300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -41879,8 +42701,1156 @@
         </is>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>3695</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>01911246556</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>DIO2U2GM3E</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:28:02</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>ZAFIRA AHMED</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>জাফিরা আহমদ</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>ZABED AHMED</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>ZAKIA FARHANA</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>Silver Bells Kindergarten &amp; Girls' High School</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>SIX</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>D6, HOUSE NO-03, LANE NO-02, ROAD NO-01, BLOCK-G, HALISHAHAR H/E, HALISHAHAR, CHATTOGRAM</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>01911246556</t>
+        </is>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>halishahar</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>3786</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>01815511550</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Humaira Jahan</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:13:22</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Humaira Jahan Rejum</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>হুমায়রা জাহান রিজুম</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>MD Shahjahan</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Mrs Halima Khatun</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>Kattali Ideal Kinder Garten And High School</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>North Kattali, Ina Gazi Bari, Akborshah, Chittagong</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>01815511550</t>
+        </is>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>halishahar</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>3834</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>01820293583</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>DJ91NISEWL</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>2026-10-10 07:25:43</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Faria Jamal</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>ফারিয়া জামাল</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>MD Jamal Uddin</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Goal Nahar</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>Feni Govt Girls High School</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>Nazir road,Feni</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>01820293583</t>
+        </is>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>halishahar</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>3862</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>01712386612</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>766LJLCV</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:20:24</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>MD. ATIQUL ALAM RAFI</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>মোঃ আতিকুল আলম রাফি</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>RUMAN</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>MONIRA</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>PRAVATI MADDHYAMIK SHIKKHA NIKETON</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>FIVE</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>CHOWDHURY VILLA, BLOCK-B, KAIBALYADHAM R/A, FIROZSHAH, CHATTOGRAM</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>01712386612</t>
+        </is>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>halishahar</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>3863</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>01712386612</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>766LNA43</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:37:42</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>TAHASAN KHONDOKAR</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>তাহসান খন্দকার</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>MD IMRAN</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>SUFIYA JAMAN JANY</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>PRAVATI MADDHYAMIK SHIKKHA NIKETON</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>FIVE</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>CDA R/A, UTTAR KATTALI, CHATTOGRAM CITY CORPORATION, CTG.</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>01866605785</t>
+        </is>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>halishahar</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>3864</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>01805414488</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>DJL3C1P8XJ</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>2026-10-21 09:00:55</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Afra Anwar</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>আফরা আনোয়ার</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>MD. Anwar Hossain</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>Nazreen Akhter</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>Dr. Khastagir Govt. Girls High School</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>5,</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>Bahaddarhat, chattogram</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>01816611258</t>
+        </is>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>dewanhat</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>3865</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>01723088207</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>DIK30j1E2N</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:54:48</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Nusaiba Tarnnum</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>নুসাইবা তারান্নুম</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Ismail jabiullah</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>Mobassera Begum</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>Nasirabad gov. girls high school.</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>Kunjachaya r/a, Bayezid Bostami</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>01755792267</t>
+        </is>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>dewanhat</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>3866</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>01817747042</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>DJL9CGDGA7</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:08:49</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Samaira Muntaha Arha</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>সামাইরা মুনতাহা আরহা</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Shahadat Hossain</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>Taohida Akter</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>Halishahar Cantonment public school and college</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>Halishahar Green View R/A road no 3</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>01678060130</t>
+        </is>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>halishahar</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>3867</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>01818022749</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>DJL6CIIU8U</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:28:27</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Mohammed Ahrar Rahman</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>মুহাম্মদ আহরার রহমান</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Mohammed Khalilur Rahman</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>Farida Yasmin</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>Chattogram Collegiate school</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>Six</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>Amena Villa.3253/G.Banarupa R/A, Loharpool Saraipara Pahartali Chattogram</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>01818022749</t>
+        </is>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>halishahar</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>3868</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>01819107308</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>DJL8CJUJXU</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:50:52</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Abdullah al farhan</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>আবদুল্লাহ আল ফারহান</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Ershad Hossain</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>Maksura jahan</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>Shah wali ullah institute</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>Seven</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>LIBERTY SQUARE, 349/392 KAPASGOLA CHATTOGRAM</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>01836232866</t>
+        </is>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>dewanhat</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>3869</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>01581416332</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:47:49</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Jannatul Ferdous</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>জান্নাতুল ফেরদৌস</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>মো. সেলিম উদ্দিন</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>জোসনা আক্তার</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>পূর্ব টাইগারপাস সরকারি প্রাথমিক বিদ্যালয়</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>মতি ঝর্ণা, লালখান বাজার, চট্টগ্রাম ।</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>01577707123</t>
+        </is>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>dewanhat</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>3871</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>01981666653</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>DJL1CSTHOL</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>2026-10-21 16:14:26</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Syed nafis fuad</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>সৈয়দ নাফিস ফুয়াদ</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Syed Nazmul huda</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>Dolna khanom</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>Halishar cantonment public school and college</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>723,London building,Baitul jannat moshjid lane kadamtali Chattogram</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>01981666653</t>
+        </is>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>dewanhat</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>3872</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>01571475611</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Mahib sw</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>2026-10-21 17:01:22</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Boy</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Imran Al Noor</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>ইমরান আল নুর</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Mohammed Noor Uddin</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>Jannatul Ferdous</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>BN School and College</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>Fajar ali sarang house, South Halishahar</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>01742688898</t>
+        </is>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>Patenga</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>3873</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>01878351990</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Ishtiaqe Mahmud</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>2026-10-21 17:19:19</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Girl</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Sabiha Kader Jahin</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>সাবিহা কাদের জাহিন</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>আব্দুল কাদের জিলানী</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>ফরিদা আখতার</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>আলহাজ ইয়াকুব আলী স্কুল এন্ড কলেজ</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>ষষ্ঠ শ্রেণি</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>১০</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>বারো কোয়াটার পাহাড়তলী চট্টগ্রাম</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>01854312371</t>
+        </is>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>halishahar</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S286"/>
+  <autoFilter ref="A1:S300"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Admit_Card_Data_2026.xlsx
+++ b/Admit_Card_Data_2026.xlsx
@@ -10468,9 +10468,14 @@
       <c r="A173" t="n">
         <v>3695</v>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>64226022</t>
+        </is>
+      </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Admit_3695</t>
+          <t>Admit_64226022</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10508,7 +10513,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>নতুন মনছুরাবাদ আলহাজ্ব মোস্তফা হাকিম হাই স্কুল</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -14528,9 +14533,14 @@
       <c r="A243" t="n">
         <v>3786</v>
       </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>94226007</t>
+        </is>
+      </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Admit_3786</t>
+          <t>Admit_94226007</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -14568,7 +14578,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>নতুন মনছুরাবাদ আলহাজ্ব মোস্তফা হাকিম হাই স্কুল</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -15799,9 +15809,14 @@
       <c r="A265" t="n">
         <v>3834</v>
       </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>94226008</t>
+        </is>
+      </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Admit_3834</t>
+          <t>Admit_94226008</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -15839,7 +15854,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>নতুন মনছুরাবাদ আলহাজ্ব মোস্তফা হাকিম হাই স্কুল</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -17191,9 +17206,14 @@
       <c r="A289" t="n">
         <v>3862</v>
       </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>54126033</t>
+        </is>
+      </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Admit_3862</t>
+          <t>Admit_54126033</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -17231,7 +17251,7 @@
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>নতুন মনছুরাবাদ আলহাজ্ব মোস্তফা হাকিম হাই স্কুল</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -17244,9 +17264,14 @@
       <c r="A290" t="n">
         <v>3863</v>
       </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>54126034</t>
+        </is>
+      </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Admit_3863</t>
+          <t>Admit_54126034</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -17284,7 +17309,7 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>নতুন মনছুরাবাদ আলহাজ্ব মোস্তফা হাকিম হাই স্কুল</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -17297,9 +17322,14 @@
       <c r="A291" t="n">
         <v>3864</v>
       </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>51226086</t>
+        </is>
+      </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Admit_3864</t>
+          <t>Admit_51226086</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -17350,9 +17380,14 @@
       <c r="A292" t="n">
         <v>3865</v>
       </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>81226036</t>
+        </is>
+      </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Admit_3865</t>
+          <t>Admit_81226036</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -17403,9 +17438,14 @@
       <c r="A293" t="n">
         <v>3866</v>
       </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>64226023</t>
+        </is>
+      </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Admit_3866</t>
+          <t>Admit_64226023</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -17443,7 +17483,7 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>নতুন মনছুরাবাদ আলহাজ্ব মোস্তফা হাকিম হাই স্কুল</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -17456,9 +17496,14 @@
       <c r="A294" t="n">
         <v>3867</v>
       </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>64126023</t>
+        </is>
+      </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Admit_3867</t>
+          <t>Admit_64126023</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -17496,7 +17541,7 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>নতুন মনছুরাবাদ আলহাজ্ব মোস্তফা হাকিম হাই স্কুল</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -17509,9 +17554,14 @@
       <c r="A295" t="n">
         <v>3868</v>
       </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>71126063</t>
+        </is>
+      </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Admit_3868</t>
+          <t>Admit_71126063</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -17562,9 +17612,14 @@
       <c r="A296" t="n">
         <v>3869</v>
       </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>41226076</t>
+        </is>
+      </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Admit_3869</t>
+          <t>Admit_41226076</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -17615,9 +17670,14 @@
       <c r="A297" t="n">
         <v>3871</v>
       </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>71126064</t>
+        </is>
+      </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Admit_3871</t>
+          <t>Admit_71126064</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -17668,9 +17728,14 @@
       <c r="A298" t="n">
         <v>3872</v>
       </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>62126078</t>
+        </is>
+      </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Admit_3872</t>
+          <t>Admit_62126078</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -17721,9 +17786,14 @@
       <c r="A299" t="n">
         <v>3873</v>
       </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>54226024</t>
+        </is>
+      </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Admit_3873</t>
+          <t>Admit_54226024</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -17761,7 +17831,7 @@
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>চট্টগ্রাম কলেজিয়েট স্কুল</t>
+          <t>নতুন মনছুরাবাদ আলহাজ্ব মোস্তফা হাকিম হাই স্কুল</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">

--- a/Admit_Card_Data_2026.xlsx
+++ b/Admit_Card_Data_2026.xlsx
@@ -17788,12 +17788,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>54226024</t>
+          <t>64226024</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Admit_54226024</t>
+          <t>Admit_64226024</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
